--- a/fin_strength_calc/PFHE_fin_calc.xlsx
+++ b/fin_strength_calc/PFHE_fin_calc.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="계산기" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="물성DB" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="좌굴스캔" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="설명" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="강도계산서" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="물성DB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="좌굴스캔" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="설명" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="T_S">물성DB!$A$6:$A$12</definedName>
@@ -33,7 +34,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -100,6 +101,50 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00333333"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000000FF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00444444"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="12"/>
     </font>
@@ -121,7 +166,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -153,8 +198,23 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F9FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -176,11 +236,25 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="001F4E78"/>
+      </left>
+      <right style="medium">
+        <color rgb="001F4E78"/>
+      </right>
+      <top style="medium">
+        <color rgb="001F4E78"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001F4E78"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -240,6 +314,101 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -251,16 +420,16 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1505,6 +1674,1300 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:H70"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="1.8" customWidth="1" min="1" max="1"/>
+    <col width="4.5" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>강 도 계 산 서   /   STRENGTH CALCULATION SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>PFHE(Brazed Aluminium Plate-Fin Heat Exchanger) Plain 핀 두께 강도 검토 · ASME Sec. VIII Div.1 / ALPEMA Standard 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>1.  문 서 정 보  (Document Information)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>프로젝트명</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr"/>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>문서번호</t>
+        </is>
+      </c>
+      <c r="G5" s="25" t="inlineStr"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>기기번호 (Item No.)</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr"/>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>Rev.</t>
+        </is>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>작성자 (Prepared by)</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr"/>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>작성일 (Date)</t>
+        </is>
+      </c>
+      <c r="G7" s="25" t="inlineStr"/>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>검토자 (Checked by)</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr"/>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>적용 코드</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t>ASME Sec. VIII Div.1 / ALPEMA 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>2.  설 계 조 건  (Design Conditions)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>항 목</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>기 호</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="G11" s="27" t="inlineStr">
+        <is>
+          <t>비 고</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="B12" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="29" t="inlineStr">
+        <is>
+          <t>설계온도</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="E12" s="30">
+        <f>계산기!$C$5</f>
+        <v/>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G12" s="28">
+        <f>IF(계산기!$C$5&gt;204,"⚠️ 재질한계 204°C 초과","≤ 204 (ALPEMA Table 6-1)")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="B13" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>핀 인장 유발 차압</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>ΔP_t</t>
+        </is>
+      </c>
+      <c r="E13" s="33">
+        <f>계산기!$C$6</f>
+        <v/>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="inlineStr">
+        <is>
+          <t>층 설계압력(MAWP), 인접층 0 가정</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="B14" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>핀 압축 유발 차압</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>ΔP_c</t>
+        </is>
+      </c>
+      <c r="E14" s="34">
+        <f>계산기!$C$7</f>
+        <v/>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="G14" s="28">
+        <f>IF(계산기!$C$7&gt;0,"인접층 가압 / 자층 감압 조건","해당 없음")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="B15" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>자층 핀 피치</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="E15" s="33">
+        <f>계산기!$C$8</f>
+        <v/>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G15" s="31">
+        <f>계산기!$C$31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="B16" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>인접층 핀 피치</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
+        <is>
+          <t>p_adj</t>
+        </is>
+      </c>
+      <c r="E16" s="34">
+        <f>계산기!$C$9</f>
+        <v/>
+      </c>
+      <c r="F16" s="28" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G16" s="28">
+        <f>IF(계산기!$C$9&gt;0,"파팅시트 스팬 지배 검토","미입력 (자층 기준)")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="B17" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>핀 높이 (=사이드바 높이)</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E17" s="35">
+        <f>계산기!$C$10</f>
+        <v/>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G17" s="31">
+        <f>계산기!$C$32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="B18" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>좌굴 유효길이계수</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="E18" s="36">
+        <f>계산기!$C$11</f>
+        <v/>
+      </c>
+      <c r="F18" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="28">
+        <f>IF(계산기!$C$11&lt;=0.7,"고정-힌지 준용 (sway 억제 전제)","보수적 적용")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="B19" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>인장 스테이 계수</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="E19" s="37">
+        <f>계산기!$C$12</f>
+        <v/>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="31">
+        <f>IF(계산기!$C$12&gt;1,"UG-50(b) 준용 (+10%)","미적용")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="B20" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" s="29" t="inlineStr">
+        <is>
+          <t>제작 공차계수</t>
+        </is>
+      </c>
+      <c r="D20" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="36">
+        <f>계산기!$C$13</f>
+        <v/>
+      </c>
+      <c r="F20" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="28">
+        <f>IF(계산기!$C$13&lt;1,"유효두께 = 공칭 × 공차계수","공차 미반영")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="B21" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>파팅시트 층간 차압</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="E21" s="33">
+        <f>계산기!$C$14</f>
+        <v/>
+      </c>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="G21" s="31" t="inlineStr">
+        <is>
+          <t>|P_A − P_B|</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="B22" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>균형가압 압력</t>
+        </is>
+      </c>
+      <c r="D22" s="28" t="inlineStr">
+        <is>
+          <t>P_min</t>
+        </is>
+      </c>
+      <c r="E22" s="34">
+        <f>계산기!$C$15</f>
+        <v/>
+      </c>
+      <c r="F22" s="28" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="G22" s="28">
+        <f>IF(계산기!$C$15&gt;0,"핀 풋 어긋남 교번하중 반영","미고려")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="B23" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>선정 핀 두께 (공칭)</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>t_sel</t>
+        </is>
+      </c>
+      <c r="E23" s="33">
+        <f>IF(계산기!$C$16&gt;0,계산기!$C$16,"—")</f>
+        <v/>
+      </c>
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G23" s="31">
+        <f>IF(계산기!$C$16&gt;0,"§5 검증 대상","미선정 — 검증 생략")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>3.  재 료 및 허 용 응 력  (Material &amp; Allowable Stress)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="B26" s="27" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C26" s="27" t="inlineStr">
+        <is>
+          <t>항 목</t>
+        </is>
+      </c>
+      <c r="D26" s="27" t="inlineStr">
+        <is>
+          <t>기 호</t>
+        </is>
+      </c>
+      <c r="E26" s="27" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="G26" s="27" t="inlineStr">
+        <is>
+          <t>출 처 / 비 고</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="B27" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>핀 재질</t>
+        </is>
+      </c>
+      <c r="D27" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="28" t="inlineStr">
+        <is>
+          <t>AL 3003-O</t>
+        </is>
+      </c>
+      <c r="F27" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" s="28" t="inlineStr">
+        <is>
+          <t>SB-209, 브레이징 후 완전 어닐링(ALPEMA 5.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="B28" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>설계온도 허용응력</t>
+        </is>
+      </c>
+      <c r="D28" s="31" t="inlineStr">
+        <is>
+          <t>S(T)</t>
+        </is>
+      </c>
+      <c r="E28" s="37">
+        <f>계산기!$C$21</f>
+        <v/>
+      </c>
+      <c r="F28" s="31" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="G28" s="31" t="inlineStr">
+        <is>
+          <t>ASME Sec. II-D Table 1B (온도 선형보간)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="B29" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>설계온도 항복강도</t>
+        </is>
+      </c>
+      <c r="D29" s="28" t="inlineStr">
+        <is>
+          <t>Sy(T)</t>
+        </is>
+      </c>
+      <c r="E29" s="36">
+        <f>계산기!$C$22</f>
+        <v/>
+      </c>
+      <c r="F29" s="28" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="G29" s="28" t="inlineStr">
+        <is>
+          <t>Johnson 비탄성 좌굴 천이용</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="B30" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>설계온도 탄성계수</t>
+        </is>
+      </c>
+      <c r="D30" s="31" t="inlineStr">
+        <is>
+          <t>E(T)</t>
+        </is>
+      </c>
+      <c r="E30" s="38">
+        <f>계산기!$C$23</f>
+        <v/>
+      </c>
+      <c r="F30" s="31" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="G30" s="31" t="inlineStr">
+        <is>
+          <t>ASME Sec. II-D TM (좌굴 임계응력용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="B31" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>포아송비</t>
+        </is>
+      </c>
+      <c r="D31" s="28" t="inlineStr">
+        <is>
+          <t>ν</t>
+        </is>
+      </c>
+      <c r="E31" s="36">
+        <f>계산기!$C$18</f>
+        <v/>
+      </c>
+      <c r="F31" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" s="28" t="inlineStr">
+        <is>
+          <t>알루미늄 합금</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="B32" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" s="32" t="inlineStr">
+        <is>
+          <t>좌굴 설계계수</t>
+        </is>
+      </c>
+      <c r="D32" s="31" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="E32" s="35">
+        <f>계산기!$C$19</f>
+        <v/>
+      </c>
+      <c r="F32" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" s="31" t="inlineStr">
+        <is>
+          <t>ASME Div.1 UG-28 철학 준용</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>4.  강 도 계 산 결 과  (Calculation Results)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>검 토 항 목</t>
+        </is>
+      </c>
+      <c r="D35" s="27" t="inlineStr">
+        <is>
+          <t>적 용 식</t>
+        </is>
+      </c>
+      <c r="E35" s="27" t="inlineStr">
+        <is>
+          <t>계산값</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="G35" s="27" t="inlineStr">
+        <is>
+          <t>기준 / 판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="B36" s="28" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="C36" s="29" t="inlineStr">
+        <is>
+          <t>핀 인장 최소두께</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="inlineStr">
+        <is>
+          <t>t ≥ f·ΔP_t·p / (S + f·ΔP_t)</t>
+        </is>
+      </c>
+      <c r="E36" s="39">
+        <f>계산기!$C$26</f>
+        <v/>
+      </c>
+      <c r="F36" s="28" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G36" s="28">
+        <f>"식(2) — 지배: "&amp;IF(계산기!$C$26&gt;=계산기!$C$27,"■ 인장 지배","인장 비지배")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="B37" s="31" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="C37" s="32" t="inlineStr">
+        <is>
+          <t>핀 좌굴 최소두께</t>
+        </is>
+      </c>
+      <c r="D37" s="40" t="inlineStr">
+        <is>
+          <t>ΔP_c·p/t ≤ min(σ_cr/DF, S)</t>
+        </is>
+      </c>
+      <c r="E37" s="41">
+        <f>계산기!$C$27</f>
+        <v/>
+      </c>
+      <c r="F37" s="31" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G37" s="31">
+        <f>IF(계산기!$C$7&lt;=0,"식(3~5) — ΔP_c=0, 해당 없음","식(3~5) Johnson 천이 — "&amp;IF(계산기!$C$27&gt;계산기!$C$26,"■ 좌굴 지배","좌굴 비지배"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="B38" s="28" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="C38" s="29" t="inlineStr">
+        <is>
+          <t>요구 핀두께 (유효)</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="inlineStr">
+        <is>
+          <t>max( 4.1 , 4.2 )</t>
+        </is>
+      </c>
+      <c r="E38" s="39">
+        <f>계산기!$C$28</f>
+        <v/>
+      </c>
+      <c r="F38" s="28" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G38" s="28" t="inlineStr">
+        <is>
+          <t>최소 보증두께 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="B39" s="31" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="C39" s="32" t="inlineStr">
+        <is>
+          <t>요구 핀두께 (공칭)</t>
+        </is>
+      </c>
+      <c r="D39" s="40" t="inlineStr">
+        <is>
+          <t>유효두께 / 공차계수</t>
+        </is>
+      </c>
+      <c r="E39" s="41">
+        <f>계산기!$C$29</f>
+        <v/>
+      </c>
+      <c r="F39" s="31" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G39" s="31">
+        <f>계산기!$C$30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="B40" s="28" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="C40" s="29" t="inlineStr">
+        <is>
+          <t>파팅시트 최소두께</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="inlineStr">
+        <is>
+          <t>t_ps ≥ √( 4·M_d / S )</t>
+        </is>
+      </c>
+      <c r="E40" s="39">
+        <f>계산기!$C$38</f>
+        <v/>
+      </c>
+      <c r="F40" s="28" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G40" s="28">
+        <f>계산기!$C$39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="B41" s="42" t="inlineStr"/>
+      <c r="C41" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (파팅시트 중간값)</t>
+        </is>
+      </c>
+      <c r="D41" s="43">
+        <f>"지배 피치 p̄ = "&amp;TEXT(계산기!$C$34,"0.000")&amp;" mm,  스팬 s = "&amp;TEXT(계산기!$C$36,"0.000")&amp;" mm"</f>
+        <v/>
+      </c>
+      <c r="E41" s="44">
+        <f>계산기!$C$37</f>
+        <v/>
+      </c>
+      <c r="F41" s="42" t="inlineStr">
+        <is>
+          <t>N·mm/mm</t>
+        </is>
+      </c>
+      <c r="G41" s="42" t="inlineStr">
+        <is>
+          <t>설계 모멘트 M_d = w·s²/12 + P_min·(p̄−t)·p̄/8</t>
+        </is>
+      </c>
+      <c r="H41" s="45" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>5.  선 정 사 양 검 증  (Verification of Selected Fin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C44" s="27" t="inlineStr">
+        <is>
+          <t>검 토 항 목</t>
+        </is>
+      </c>
+      <c r="D44" s="27" t="inlineStr">
+        <is>
+          <t>적 용 식</t>
+        </is>
+      </c>
+      <c r="E44" s="27" t="inlineStr">
+        <is>
+          <t>계산 응력</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="inlineStr">
+        <is>
+          <t>허용 응력</t>
+        </is>
+      </c>
+      <c r="G44" s="27" t="inlineStr">
+        <is>
+          <t>안전율 SF</t>
+        </is>
+      </c>
+      <c r="H44" s="27" t="inlineStr">
+        <is>
+          <t>판 정</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="B45" s="28" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="C45" s="29" t="inlineStr">
+        <is>
+          <t>핀 인장 응력</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="inlineStr">
+        <is>
+          <t>f·σ_t = f·ΔP_t·(p−t)/t</t>
+        </is>
+      </c>
+      <c r="E45" s="36">
+        <f>IF(계산기!$C$42="","—",계산기!$C$42)</f>
+        <v/>
+      </c>
+      <c r="F45" s="36">
+        <f>계산기!$C$21</f>
+        <v/>
+      </c>
+      <c r="G45" s="36">
+        <f>IF(AND(ISNUMBER(계산기!$C$42),계산기!$C$42&gt;0),계산기!$C$21/계산기!$C$42,"—")</f>
+        <v/>
+      </c>
+      <c r="H45" s="28">
+        <f>IF(계산기!$C$43="","—",계산기!$C$43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="B46" s="31" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="C46" s="32" t="inlineStr">
+        <is>
+          <t>핀 압축·좌굴 응력</t>
+        </is>
+      </c>
+      <c r="D46" s="40" t="inlineStr">
+        <is>
+          <t>σ_c = ΔP_c·p/t</t>
+        </is>
+      </c>
+      <c r="E46" s="37">
+        <f>IF(계산기!$C$44="","—",계산기!$C$44)</f>
+        <v/>
+      </c>
+      <c r="F46" s="37">
+        <f>IF(계산기!$C$46="","—",계산기!$C$46)</f>
+        <v/>
+      </c>
+      <c r="G46" s="37">
+        <f>IF(AND(ISNUMBER(계산기!$C$44),계산기!$C$44&gt;0),계산기!$C$46/계산기!$C$44,"—")</f>
+        <v/>
+      </c>
+      <c r="H46" s="31">
+        <f>IF(계산기!$C$47="","—",계산기!$C$47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="B47" s="28" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="C47" s="29" t="inlineStr">
+        <is>
+          <t>핀 두께 여유</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>유효 t / 요구 t (유효 기준)</t>
+        </is>
+      </c>
+      <c r="E47" s="34">
+        <f>IF(계산기!$C$16&gt;0,계산기!$C$41,"—")</f>
+        <v/>
+      </c>
+      <c r="F47" s="34">
+        <f>계산기!$C$28</f>
+        <v/>
+      </c>
+      <c r="G47" s="36">
+        <f>IF(AND(계산기!$C$16&gt;0,계산기!$C$28&gt;0),계산기!$C$41/계산기!$C$28,"—")</f>
+        <v/>
+      </c>
+      <c r="H47" s="28">
+        <f>IF(계산기!$C$16&lt;=0,"—",IF(계산기!$C$41&gt;=계산기!$C$28,"합격 ✓","불합격 ✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="B48" s="46" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="C48" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (참고) 좌굴 임계응력</t>
+        </is>
+      </c>
+      <c r="D48" s="47" t="inlineStr">
+        <is>
+          <t>σ_cr : Johnson 포물선 천이 적용</t>
+        </is>
+      </c>
+      <c r="E48" s="48">
+        <f>IF(계산기!$C$45="","—",계산기!$C$45)</f>
+        <v/>
+      </c>
+      <c r="F48" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="48">
+        <f>IF(AND(ISNUMBER(계산기!$C$45),계산기!$C$44&gt;0),계산기!$C$45/계산기!$C$44,"—")</f>
+        <v/>
+      </c>
+      <c r="H48" s="46" t="inlineStr">
+        <is>
+          <t>참고값</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>6.  결 론  (Conclusion)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="B51" s="49">
+        <f>"1)  설계조건 — 설계온도 "&amp;TEXT(계산기!$C$5,"0")&amp;" °C, 인장차압 ΔP_t = "&amp;TEXT(계산기!$C$6,"0.000")&amp;" MPa, 압축차압 ΔP_c = "&amp;TEXT(계산기!$C$7,"0.000")&amp;" MPa, 핀 피치 "&amp;TEXT(계산기!$C$8,"0.000")&amp;" mm, 핀 높이 "&amp;TEXT(계산기!$C$10,"0.0")&amp;" mm."</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="B52" s="49">
+        <f>"2)  허용응력 S(T) = "&amp;TEXT(계산기!$C$21,"0.00")&amp;" MPa (AL 3003-O, ASME Sec. II-D) 기준, 요구 핀두께는 "&amp;IF(ISNUMBER(계산기!$C$29),TEXT(계산기!$C$29,"0.000")&amp;" mm (공칭)",계산기!$C$29)&amp;" 이며 ALPEMA 제작범위(0.15~0.7 mm) 대비 "&amp;계산기!$C$30&amp;" 이다."</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="B53" s="49">
+        <f>"3)  파팅시트 최소두께는 "&amp;IF(ISNUMBER(계산기!$C$38),TEXT(계산기!$C$38,"0.000")&amp;" mm",계산기!$C$38)&amp;" 이며, ALPEMA 표준범위(0.8~2.0 mm) 대비 "&amp;계산기!$C$39&amp;" 이다."</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="B54" s="49">
+        <f>"4)  선정 핀두께 "&amp;IF(계산기!$C$16&gt;0,TEXT(계산기!$C$16,"0.000")&amp;" mm (유효 "&amp;TEXT(계산기!$C$41,"0.000")&amp;" mm)","(미선정)")&amp;" 에 대한 응력 검증 결과 — 인장 "&amp;IF(계산기!$C$16&gt;0,계산기!$C$43,"생략")&amp;IF(계산기!$C$7&gt;0,", 압축·좌굴 "&amp;IF(계산기!$C$16&gt;0,계산기!$C$47,"생략"),"")&amp;" 로 평가되었다."</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="26" customHeight="1">
+      <c r="B56" s="50">
+        <f>"■  최 종 판 정  :   "&amp;계산기!$C$48&amp;IF(계산기!$C$5&gt;204,"   (설계온도 재질한계 초과 — 결과 무효)","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="23" t="inlineStr">
+        <is>
+          <t>7.  적 용 기 준 및 한 계  (Basis &amp; Limitations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="13" customHeight="1">
+      <c r="B59" s="51" t="inlineStr">
+        <is>
+          <t>· 본 계산서는 예비설계용이다. 인증 설계는 ALPEMA 5.15.1.1(코드 당국 승인 계산법) 또는 5.15.1.2(파열시험)로 확정하여야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="13" customHeight="1">
+      <c r="B60" s="51" t="inlineStr">
+        <is>
+          <t>· 정적 압력하중 전용 — 열응력·피로는 ALPEMA 8.1의 운전 제한(±1 °C/min 등)으로 별도 관리한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="13" customHeight="1">
+      <c r="B61" s="51" t="inlineStr">
+        <is>
+          <t>· 허용응력 S(T)·항복강도 Sy(T)·탄성계수 E(T)는 대표값이며, 적용 코드 연도판의 ASME Sec. II-D 값으로 검증·교체하여야 한다. ([물성DB] 시트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="13" customHeight="1">
+      <c r="B62" s="51" t="inlineStr">
+        <is>
+          <t>· 149 °C 이상 장기 운전은 크리프 영향으로 별도 검토가 필요하다. 204 °C 초과는 3003 재질 적용범위 밖이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="13" customHeight="1">
+      <c r="B63" s="51" t="inlineStr">
+        <is>
+          <t>· 대상은 Plain 핀에 한한다. Serrated·Perforated 핀, 디스트리뷰터 핀, 헤더·노즐부는 범위 밖이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="13" customHeight="1">
+      <c r="B64" s="51" t="inlineStr">
+        <is>
+          <t>· 인접층 압력은 신뢰할 수 있는 감압 방지 수단이 없는 한 0(대기압)으로 가정하였다 (ALPEMA 5.6.1 개별 챔버 가압 / 5.6.2.1 단일 챔버 설계압력 근거).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="13" customHeight="1">
+      <c r="B65" s="51" t="inlineStr">
+        <is>
+          <t>· 상세 유도 근거: fin_thickness_derivation.md,  계산 로직 원본: fin_thickness_calc.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="B67" s="27" t="inlineStr"/>
+      <c r="C67" s="27" t="inlineStr">
+        <is>
+          <t>작 성 (Prepared)</t>
+        </is>
+      </c>
+      <c r="D67" s="27" t="inlineStr">
+        <is>
+          <t>검 토 (Checked)</t>
+        </is>
+      </c>
+      <c r="F67" s="27" t="inlineStr"/>
+      <c r="G67" s="27" t="inlineStr">
+        <is>
+          <t>승 인 (Approved)</t>
+        </is>
+      </c>
+      <c r="H67" s="27" t="inlineStr">
+        <is>
+          <t>일 자 (Date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="34" customHeight="1">
+      <c r="B68" s="52" t="n"/>
+      <c r="C68" s="52" t="n"/>
+      <c r="D68" s="52" t="n"/>
+      <c r="F68" s="52" t="n"/>
+      <c r="G68" s="52" t="n"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="53">
+        <f>"본 계산서는 [계산기] 시트의 입력값에 연동되어 자동 산출됨.   적용 코드: ASME Sec. VIII Div.1 · ALPEMA Standard 2024   |   재질: AL 3003-O   |   단위: MPa, mm"</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="65">
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="B64:H64"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B51:H51"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="B63:H63"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B50:H50"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="C68"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B70:H70"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="B60:H60"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="B34:H34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H12"/>
@@ -1519,169 +2982,169 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="54" t="inlineStr">
         <is>
           <t>재료 물성 데이터 — AL 3003-O (ASME Sec. II-D 대표값)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="55" t="inlineStr">
         <is>
           <t>⚠️ 대표값 — 실제 설계 전 적용 코드 연도판 값으로 교체할 것. 온도 오름차순 유지.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="56" t="inlineStr">
         <is>
           <t>허용응력 S(T)</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="56" t="inlineStr">
         <is>
           <t>항복강도 Sy(T)</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="56" t="inlineStr">
         <is>
           <t>탄성계수 E(T)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="57" t="inlineStr">
         <is>
           <t>온도(°C)</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="57" t="inlineStr">
         <is>
           <t>S (MPa)</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="57" t="inlineStr">
         <is>
           <t>온도(°C)</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="57" t="inlineStr">
         <is>
           <t>Sy (MPa)</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="57" t="inlineStr">
         <is>
           <t>온도(°C)</t>
         </is>
       </c>
-      <c r="H5" s="24" t="inlineStr">
+      <c r="H5" s="57" t="inlineStr">
         <is>
           <t>E (MPa)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="n">
+      <c r="A6" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="58" t="n">
         <v>22.8</v>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="58" t="n">
         <v>34.5</v>
       </c>
-      <c r="G6" s="25" t="n">
+      <c r="G6" s="58" t="n">
         <v>25</v>
       </c>
-      <c r="H6" s="25" t="n">
+      <c r="H6" s="58" t="n">
         <v>68900</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="n">
+      <c r="A7" s="58" t="n">
         <v>65</v>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="58" t="n">
         <v>22.8</v>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="58" t="n">
         <v>93</v>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="58" t="n">
         <v>33.1</v>
       </c>
-      <c r="G7" s="25" t="n">
+      <c r="G7" s="58" t="n">
         <v>93</v>
       </c>
-      <c r="H7" s="25" t="n">
+      <c r="H7" s="58" t="n">
         <v>66200</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="n">
+      <c r="A8" s="58" t="n">
         <v>93</v>
       </c>
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="58" t="n">
         <v>22.6</v>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="58" t="n">
         <v>149</v>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="58" t="n">
         <v>29.6</v>
       </c>
-      <c r="G8" s="25" t="n">
+      <c r="G8" s="58" t="n">
         <v>149</v>
       </c>
-      <c r="H8" s="25" t="n">
+      <c r="H8" s="58" t="n">
         <v>63400</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="n">
+      <c r="A9" s="58" t="n">
         <v>121</v>
       </c>
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="58" t="n">
         <v>21.4</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="58" t="n">
         <v>204</v>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="58" t="n">
         <v>24.1</v>
       </c>
-      <c r="G9" s="25" t="n">
+      <c r="G9" s="58" t="n">
         <v>204</v>
       </c>
-      <c r="H9" s="25" t="n">
+      <c r="H9" s="58" t="n">
         <v>60000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="n">
+      <c r="A10" s="58" t="n">
         <v>149</v>
       </c>
-      <c r="B10" s="25" t="n">
+      <c r="B10" s="58" t="n">
         <v>18.6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="n">
+      <c r="A11" s="58" t="n">
         <v>177</v>
       </c>
-      <c r="B11" s="25" t="n">
+      <c r="B11" s="58" t="n">
         <v>14.5</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="n">
+      <c r="A12" s="58" t="n">
         <v>204</v>
       </c>
-      <c r="B12" s="25" t="n">
+      <c r="B12" s="58" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1690,7 +3153,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1708,32 +3171,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>t 후보(mm)</t>
         </is>
       </c>
-      <c r="B1" s="24" t="inlineStr">
+      <c r="B1" s="57" t="inlineStr">
         <is>
           <t>σ_c(MPa)</t>
         </is>
       </c>
-      <c r="C1" s="24" t="inlineStr">
+      <c r="C1" s="57" t="inlineStr">
         <is>
           <t>σ_cr,E(MPa)</t>
         </is>
       </c>
-      <c r="D1" s="24" t="inlineStr">
+      <c r="D1" s="57" t="inlineStr">
         <is>
           <t>σ_cr Johnson(MPa)</t>
         </is>
       </c>
-      <c r="E1" s="24" t="inlineStr">
+      <c r="E1" s="57" t="inlineStr">
         <is>
           <t>허용(MPa)</t>
         </is>
       </c>
-      <c r="F1" s="24" t="inlineStr">
+      <c r="F1" s="57" t="inlineStr">
         <is>
           <t>OK(1/0)</t>
         </is>
@@ -1745,22 +3208,22 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="n">
+      <c r="A2" s="59" t="n">
         <v>0.01</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="60">
         <f>계산기!$C$7*계산기!$C$8/A2</f>
         <v/>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A2/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D2" s="27">
+      <c r="D2" s="60">
         <f>IF(C2&lt;=계산기!$C$22/2,C2,계산기!$C$22*(1-계산기!$C$22/(4*C2)))</f>
         <v/>
       </c>
-      <c r="E2" s="27">
+      <c r="E2" s="60">
         <f>MIN(D2/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -1770,22 +3233,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="n">
+      <c r="A3" s="59" t="n">
         <v>0.015</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="60">
         <f>계산기!$C$7*계산기!$C$8/A3</f>
         <v/>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A3/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="60">
         <f>IF(C3&lt;=계산기!$C$22/2,C3,계산기!$C$22*(1-계산기!$C$22/(4*C3)))</f>
         <v/>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="60">
         <f>MIN(D3/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -1795,22 +3258,22 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="n">
+      <c r="A4" s="59" t="n">
         <v>0.02</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="60">
         <f>계산기!$C$7*계산기!$C$8/A4</f>
         <v/>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A4/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="60">
         <f>IF(C4&lt;=계산기!$C$22/2,C4,계산기!$C$22*(1-계산기!$C$22/(4*C4)))</f>
         <v/>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="60">
         <f>MIN(D4/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -1820,22 +3283,22 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="n">
+      <c r="A5" s="59" t="n">
         <v>0.025</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="60">
         <f>계산기!$C$7*계산기!$C$8/A5</f>
         <v/>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A5/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="60">
         <f>IF(C5&lt;=계산기!$C$22/2,C5,계산기!$C$22*(1-계산기!$C$22/(4*C5)))</f>
         <v/>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="60">
         <f>MIN(D5/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -1845,22 +3308,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="59" t="n">
         <v>0.03</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="60">
         <f>계산기!$C$7*계산기!$C$8/A6</f>
         <v/>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A6/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="60">
         <f>IF(C6&lt;=계산기!$C$22/2,C6,계산기!$C$22*(1-계산기!$C$22/(4*C6)))</f>
         <v/>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="60">
         <f>MIN(D6/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -1870,22 +3333,22 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="59" t="n">
         <v>0.035</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="60">
         <f>계산기!$C$7*계산기!$C$8/A7</f>
         <v/>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A7/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="60">
         <f>IF(C7&lt;=계산기!$C$22/2,C7,계산기!$C$22*(1-계산기!$C$22/(4*C7)))</f>
         <v/>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="60">
         <f>MIN(D7/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -1895,22 +3358,22 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="59" t="n">
         <v>0.04</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="60">
         <f>계산기!$C$7*계산기!$C$8/A8</f>
         <v/>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A8/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="60">
         <f>IF(C8&lt;=계산기!$C$22/2,C8,계산기!$C$22*(1-계산기!$C$22/(4*C8)))</f>
         <v/>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="60">
         <f>MIN(D8/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -1920,22 +3383,22 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="59" t="n">
         <v>0.045</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="60">
         <f>계산기!$C$7*계산기!$C$8/A9</f>
         <v/>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A9/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="60">
         <f>IF(C9&lt;=계산기!$C$22/2,C9,계산기!$C$22*(1-계산기!$C$22/(4*C9)))</f>
         <v/>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="60">
         <f>MIN(D9/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -1945,22 +3408,22 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="59" t="n">
         <v>0.05</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="60">
         <f>계산기!$C$7*계산기!$C$8/A10</f>
         <v/>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A10/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="60">
         <f>IF(C10&lt;=계산기!$C$22/2,C10,계산기!$C$22*(1-계산기!$C$22/(4*C10)))</f>
         <v/>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="60">
         <f>MIN(D10/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -1970,22 +3433,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="n">
+      <c r="A11" s="59" t="n">
         <v>0.055</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="60">
         <f>계산기!$C$7*계산기!$C$8/A11</f>
         <v/>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A11/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="60">
         <f>IF(C11&lt;=계산기!$C$22/2,C11,계산기!$C$22*(1-계산기!$C$22/(4*C11)))</f>
         <v/>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="60">
         <f>MIN(D11/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -1995,22 +3458,22 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="n">
+      <c r="A12" s="59" t="n">
         <v>0.06</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="60">
         <f>계산기!$C$7*계산기!$C$8/A12</f>
         <v/>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A12/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="60">
         <f>IF(C12&lt;=계산기!$C$22/2,C12,계산기!$C$22*(1-계산기!$C$22/(4*C12)))</f>
         <v/>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="60">
         <f>MIN(D12/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2020,22 +3483,22 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="n">
+      <c r="A13" s="59" t="n">
         <v>0.065</v>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="60">
         <f>계산기!$C$7*계산기!$C$8/A13</f>
         <v/>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A13/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="60">
         <f>IF(C13&lt;=계산기!$C$22/2,C13,계산기!$C$22*(1-계산기!$C$22/(4*C13)))</f>
         <v/>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="60">
         <f>MIN(D13/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2045,22 +3508,22 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="n">
+      <c r="A14" s="59" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="60">
         <f>계산기!$C$7*계산기!$C$8/A14</f>
         <v/>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A14/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="60">
         <f>IF(C14&lt;=계산기!$C$22/2,C14,계산기!$C$22*(1-계산기!$C$22/(4*C14)))</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="60">
         <f>MIN(D14/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2070,22 +3533,22 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="n">
+      <c r="A15" s="59" t="n">
         <v>0.075</v>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="60">
         <f>계산기!$C$7*계산기!$C$8/A15</f>
         <v/>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A15/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="60">
         <f>IF(C15&lt;=계산기!$C$22/2,C15,계산기!$C$22*(1-계산기!$C$22/(4*C15)))</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="60">
         <f>MIN(D15/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2095,22 +3558,22 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="n">
+      <c r="A16" s="59" t="n">
         <v>0.08</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="60">
         <f>계산기!$C$7*계산기!$C$8/A16</f>
         <v/>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A16/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="60">
         <f>IF(C16&lt;=계산기!$C$22/2,C16,계산기!$C$22*(1-계산기!$C$22/(4*C16)))</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="60">
         <f>MIN(D16/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2120,22 +3583,22 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="n">
+      <c r="A17" s="59" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="60">
         <f>계산기!$C$7*계산기!$C$8/A17</f>
         <v/>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A17/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="60">
         <f>IF(C17&lt;=계산기!$C$22/2,C17,계산기!$C$22*(1-계산기!$C$22/(4*C17)))</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="60">
         <f>MIN(D17/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2145,22 +3608,22 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="n">
+      <c r="A18" s="59" t="n">
         <v>0.09</v>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="60">
         <f>계산기!$C$7*계산기!$C$8/A18</f>
         <v/>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A18/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="60">
         <f>IF(C18&lt;=계산기!$C$22/2,C18,계산기!$C$22*(1-계산기!$C$22/(4*C18)))</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="60">
         <f>MIN(D18/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2170,22 +3633,22 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="n">
+      <c r="A19" s="59" t="n">
         <v>0.095</v>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="60">
         <f>계산기!$C$7*계산기!$C$8/A19</f>
         <v/>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A19/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="60">
         <f>IF(C19&lt;=계산기!$C$22/2,C19,계산기!$C$22*(1-계산기!$C$22/(4*C19)))</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="60">
         <f>MIN(D19/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2195,22 +3658,22 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="n">
+      <c r="A20" s="59" t="n">
         <v>0.1</v>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="60">
         <f>계산기!$C$7*계산기!$C$8/A20</f>
         <v/>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A20/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="60">
         <f>IF(C20&lt;=계산기!$C$22/2,C20,계산기!$C$22*(1-계산기!$C$22/(4*C20)))</f>
         <v/>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="60">
         <f>MIN(D20/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2220,22 +3683,22 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="n">
+      <c r="A21" s="59" t="n">
         <v>0.105</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="60">
         <f>계산기!$C$7*계산기!$C$8/A21</f>
         <v/>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A21/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="60">
         <f>IF(C21&lt;=계산기!$C$22/2,C21,계산기!$C$22*(1-계산기!$C$22/(4*C21)))</f>
         <v/>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="60">
         <f>MIN(D21/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2245,22 +3708,22 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="n">
+      <c r="A22" s="59" t="n">
         <v>0.11</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="60">
         <f>계산기!$C$7*계산기!$C$8/A22</f>
         <v/>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A22/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="60">
         <f>IF(C22&lt;=계산기!$C$22/2,C22,계산기!$C$22*(1-계산기!$C$22/(4*C22)))</f>
         <v/>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="60">
         <f>MIN(D22/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2270,22 +3733,22 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="26" t="n">
+      <c r="A23" s="59" t="n">
         <v>0.115</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="60">
         <f>계산기!$C$7*계산기!$C$8/A23</f>
         <v/>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A23/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="60">
         <f>IF(C23&lt;=계산기!$C$22/2,C23,계산기!$C$22*(1-계산기!$C$22/(4*C23)))</f>
         <v/>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="60">
         <f>MIN(D23/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2295,22 +3758,22 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="n">
+      <c r="A24" s="59" t="n">
         <v>0.12</v>
       </c>
-      <c r="B24" s="27">
+      <c r="B24" s="60">
         <f>계산기!$C$7*계산기!$C$8/A24</f>
         <v/>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A24/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="60">
         <f>IF(C24&lt;=계산기!$C$22/2,C24,계산기!$C$22*(1-계산기!$C$22/(4*C24)))</f>
         <v/>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="60">
         <f>MIN(D24/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2320,22 +3783,22 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="26" t="n">
+      <c r="A25" s="59" t="n">
         <v>0.125</v>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="60">
         <f>계산기!$C$7*계산기!$C$8/A25</f>
         <v/>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A25/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="60">
         <f>IF(C25&lt;=계산기!$C$22/2,C25,계산기!$C$22*(1-계산기!$C$22/(4*C25)))</f>
         <v/>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="60">
         <f>MIN(D25/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2345,22 +3808,22 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="26" t="n">
+      <c r="A26" s="59" t="n">
         <v>0.13</v>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="60">
         <f>계산기!$C$7*계산기!$C$8/A26</f>
         <v/>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A26/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="60">
         <f>IF(C26&lt;=계산기!$C$22/2,C26,계산기!$C$22*(1-계산기!$C$22/(4*C26)))</f>
         <v/>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="60">
         <f>MIN(D26/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2370,22 +3833,22 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="26" t="n">
+      <c r="A27" s="59" t="n">
         <v>0.135</v>
       </c>
-      <c r="B27" s="27">
+      <c r="B27" s="60">
         <f>계산기!$C$7*계산기!$C$8/A27</f>
         <v/>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A27/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="60">
         <f>IF(C27&lt;=계산기!$C$22/2,C27,계산기!$C$22*(1-계산기!$C$22/(4*C27)))</f>
         <v/>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="60">
         <f>MIN(D27/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2395,22 +3858,22 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="26" t="n">
+      <c r="A28" s="59" t="n">
         <v>0.14</v>
       </c>
-      <c r="B28" s="27">
+      <c r="B28" s="60">
         <f>계산기!$C$7*계산기!$C$8/A28</f>
         <v/>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A28/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="60">
         <f>IF(C28&lt;=계산기!$C$22/2,C28,계산기!$C$22*(1-계산기!$C$22/(4*C28)))</f>
         <v/>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="60">
         <f>MIN(D28/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2420,22 +3883,22 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="26" t="n">
+      <c r="A29" s="59" t="n">
         <v>0.145</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="60">
         <f>계산기!$C$7*계산기!$C$8/A29</f>
         <v/>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A29/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="60">
         <f>IF(C29&lt;=계산기!$C$22/2,C29,계산기!$C$22*(1-계산기!$C$22/(4*C29)))</f>
         <v/>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="60">
         <f>MIN(D29/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2445,22 +3908,22 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="n">
+      <c r="A30" s="59" t="n">
         <v>0.15</v>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="60">
         <f>계산기!$C$7*계산기!$C$8/A30</f>
         <v/>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A30/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="60">
         <f>IF(C30&lt;=계산기!$C$22/2,C30,계산기!$C$22*(1-계산기!$C$22/(4*C30)))</f>
         <v/>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="60">
         <f>MIN(D30/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2470,22 +3933,22 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26" t="n">
+      <c r="A31" s="59" t="n">
         <v>0.155</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="60">
         <f>계산기!$C$7*계산기!$C$8/A31</f>
         <v/>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A31/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="60">
         <f>IF(C31&lt;=계산기!$C$22/2,C31,계산기!$C$22*(1-계산기!$C$22/(4*C31)))</f>
         <v/>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="60">
         <f>MIN(D31/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2495,22 +3958,22 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="n">
+      <c r="A32" s="59" t="n">
         <v>0.16</v>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="60">
         <f>계산기!$C$7*계산기!$C$8/A32</f>
         <v/>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A32/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="60">
         <f>IF(C32&lt;=계산기!$C$22/2,C32,계산기!$C$22*(1-계산기!$C$22/(4*C32)))</f>
         <v/>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="60">
         <f>MIN(D32/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2520,22 +3983,22 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="26" t="n">
+      <c r="A33" s="59" t="n">
         <v>0.165</v>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="60">
         <f>계산기!$C$7*계산기!$C$8/A33</f>
         <v/>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A33/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="60">
         <f>IF(C33&lt;=계산기!$C$22/2,C33,계산기!$C$22*(1-계산기!$C$22/(4*C33)))</f>
         <v/>
       </c>
-      <c r="E33" s="27">
+      <c r="E33" s="60">
         <f>MIN(D33/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2545,22 +4008,22 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26" t="n">
+      <c r="A34" s="59" t="n">
         <v>0.17</v>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="60">
         <f>계산기!$C$7*계산기!$C$8/A34</f>
         <v/>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A34/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="60">
         <f>IF(C34&lt;=계산기!$C$22/2,C34,계산기!$C$22*(1-계산기!$C$22/(4*C34)))</f>
         <v/>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="60">
         <f>MIN(D34/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2570,22 +4033,22 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="26" t="n">
+      <c r="A35" s="59" t="n">
         <v>0.175</v>
       </c>
-      <c r="B35" s="27">
+      <c r="B35" s="60">
         <f>계산기!$C$7*계산기!$C$8/A35</f>
         <v/>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A35/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="60">
         <f>IF(C35&lt;=계산기!$C$22/2,C35,계산기!$C$22*(1-계산기!$C$22/(4*C35)))</f>
         <v/>
       </c>
-      <c r="E35" s="27">
+      <c r="E35" s="60">
         <f>MIN(D35/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2595,22 +4058,22 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="26" t="n">
+      <c r="A36" s="59" t="n">
         <v>0.18</v>
       </c>
-      <c r="B36" s="27">
+      <c r="B36" s="60">
         <f>계산기!$C$7*계산기!$C$8/A36</f>
         <v/>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A36/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D36" s="27">
+      <c r="D36" s="60">
         <f>IF(C36&lt;=계산기!$C$22/2,C36,계산기!$C$22*(1-계산기!$C$22/(4*C36)))</f>
         <v/>
       </c>
-      <c r="E36" s="27">
+      <c r="E36" s="60">
         <f>MIN(D36/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2620,22 +4083,22 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="26" t="n">
+      <c r="A37" s="59" t="n">
         <v>0.185</v>
       </c>
-      <c r="B37" s="27">
+      <c r="B37" s="60">
         <f>계산기!$C$7*계산기!$C$8/A37</f>
         <v/>
       </c>
-      <c r="C37" s="27">
+      <c r="C37" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A37/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="60">
         <f>IF(C37&lt;=계산기!$C$22/2,C37,계산기!$C$22*(1-계산기!$C$22/(4*C37)))</f>
         <v/>
       </c>
-      <c r="E37" s="27">
+      <c r="E37" s="60">
         <f>MIN(D37/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2645,22 +4108,22 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="26" t="n">
+      <c r="A38" s="59" t="n">
         <v>0.19</v>
       </c>
-      <c r="B38" s="27">
+      <c r="B38" s="60">
         <f>계산기!$C$7*계산기!$C$8/A38</f>
         <v/>
       </c>
-      <c r="C38" s="27">
+      <c r="C38" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A38/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D38" s="27">
+      <c r="D38" s="60">
         <f>IF(C38&lt;=계산기!$C$22/2,C38,계산기!$C$22*(1-계산기!$C$22/(4*C38)))</f>
         <v/>
       </c>
-      <c r="E38" s="27">
+      <c r="E38" s="60">
         <f>MIN(D38/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2670,22 +4133,22 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="26" t="n">
+      <c r="A39" s="59" t="n">
         <v>0.195</v>
       </c>
-      <c r="B39" s="27">
+      <c r="B39" s="60">
         <f>계산기!$C$7*계산기!$C$8/A39</f>
         <v/>
       </c>
-      <c r="C39" s="27">
+      <c r="C39" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A39/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D39" s="27">
+      <c r="D39" s="60">
         <f>IF(C39&lt;=계산기!$C$22/2,C39,계산기!$C$22*(1-계산기!$C$22/(4*C39)))</f>
         <v/>
       </c>
-      <c r="E39" s="27">
+      <c r="E39" s="60">
         <f>MIN(D39/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2695,22 +4158,22 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="26" t="n">
+      <c r="A40" s="59" t="n">
         <v>0.2</v>
       </c>
-      <c r="B40" s="27">
+      <c r="B40" s="60">
         <f>계산기!$C$7*계산기!$C$8/A40</f>
         <v/>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A40/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D40" s="27">
+      <c r="D40" s="60">
         <f>IF(C40&lt;=계산기!$C$22/2,C40,계산기!$C$22*(1-계산기!$C$22/(4*C40)))</f>
         <v/>
       </c>
-      <c r="E40" s="27">
+      <c r="E40" s="60">
         <f>MIN(D40/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2720,22 +4183,22 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="26" t="n">
+      <c r="A41" s="59" t="n">
         <v>0.205</v>
       </c>
-      <c r="B41" s="27">
+      <c r="B41" s="60">
         <f>계산기!$C$7*계산기!$C$8/A41</f>
         <v/>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A41/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D41" s="27">
+      <c r="D41" s="60">
         <f>IF(C41&lt;=계산기!$C$22/2,C41,계산기!$C$22*(1-계산기!$C$22/(4*C41)))</f>
         <v/>
       </c>
-      <c r="E41" s="27">
+      <c r="E41" s="60">
         <f>MIN(D41/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2745,22 +4208,22 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="26" t="n">
+      <c r="A42" s="59" t="n">
         <v>0.21</v>
       </c>
-      <c r="B42" s="27">
+      <c r="B42" s="60">
         <f>계산기!$C$7*계산기!$C$8/A42</f>
         <v/>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A42/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D42" s="27">
+      <c r="D42" s="60">
         <f>IF(C42&lt;=계산기!$C$22/2,C42,계산기!$C$22*(1-계산기!$C$22/(4*C42)))</f>
         <v/>
       </c>
-      <c r="E42" s="27">
+      <c r="E42" s="60">
         <f>MIN(D42/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2770,22 +4233,22 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="26" t="n">
+      <c r="A43" s="59" t="n">
         <v>0.215</v>
       </c>
-      <c r="B43" s="27">
+      <c r="B43" s="60">
         <f>계산기!$C$7*계산기!$C$8/A43</f>
         <v/>
       </c>
-      <c r="C43" s="27">
+      <c r="C43" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A43/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D43" s="27">
+      <c r="D43" s="60">
         <f>IF(C43&lt;=계산기!$C$22/2,C43,계산기!$C$22*(1-계산기!$C$22/(4*C43)))</f>
         <v/>
       </c>
-      <c r="E43" s="27">
+      <c r="E43" s="60">
         <f>MIN(D43/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2795,22 +4258,22 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="26" t="n">
+      <c r="A44" s="59" t="n">
         <v>0.22</v>
       </c>
-      <c r="B44" s="27">
+      <c r="B44" s="60">
         <f>계산기!$C$7*계산기!$C$8/A44</f>
         <v/>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A44/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D44" s="27">
+      <c r="D44" s="60">
         <f>IF(C44&lt;=계산기!$C$22/2,C44,계산기!$C$22*(1-계산기!$C$22/(4*C44)))</f>
         <v/>
       </c>
-      <c r="E44" s="27">
+      <c r="E44" s="60">
         <f>MIN(D44/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2820,22 +4283,22 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="26" t="n">
+      <c r="A45" s="59" t="n">
         <v>0.225</v>
       </c>
-      <c r="B45" s="27">
+      <c r="B45" s="60">
         <f>계산기!$C$7*계산기!$C$8/A45</f>
         <v/>
       </c>
-      <c r="C45" s="27">
+      <c r="C45" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A45/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D45" s="27">
+      <c r="D45" s="60">
         <f>IF(C45&lt;=계산기!$C$22/2,C45,계산기!$C$22*(1-계산기!$C$22/(4*C45)))</f>
         <v/>
       </c>
-      <c r="E45" s="27">
+      <c r="E45" s="60">
         <f>MIN(D45/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2845,22 +4308,22 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="26" t="n">
+      <c r="A46" s="59" t="n">
         <v>0.23</v>
       </c>
-      <c r="B46" s="27">
+      <c r="B46" s="60">
         <f>계산기!$C$7*계산기!$C$8/A46</f>
         <v/>
       </c>
-      <c r="C46" s="27">
+      <c r="C46" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A46/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D46" s="27">
+      <c r="D46" s="60">
         <f>IF(C46&lt;=계산기!$C$22/2,C46,계산기!$C$22*(1-계산기!$C$22/(4*C46)))</f>
         <v/>
       </c>
-      <c r="E46" s="27">
+      <c r="E46" s="60">
         <f>MIN(D46/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2870,22 +4333,22 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="26" t="n">
+      <c r="A47" s="59" t="n">
         <v>0.235</v>
       </c>
-      <c r="B47" s="27">
+      <c r="B47" s="60">
         <f>계산기!$C$7*계산기!$C$8/A47</f>
         <v/>
       </c>
-      <c r="C47" s="27">
+      <c r="C47" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A47/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D47" s="27">
+      <c r="D47" s="60">
         <f>IF(C47&lt;=계산기!$C$22/2,C47,계산기!$C$22*(1-계산기!$C$22/(4*C47)))</f>
         <v/>
       </c>
-      <c r="E47" s="27">
+      <c r="E47" s="60">
         <f>MIN(D47/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2895,22 +4358,22 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="26" t="n">
+      <c r="A48" s="59" t="n">
         <v>0.24</v>
       </c>
-      <c r="B48" s="27">
+      <c r="B48" s="60">
         <f>계산기!$C$7*계산기!$C$8/A48</f>
         <v/>
       </c>
-      <c r="C48" s="27">
+      <c r="C48" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A48/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D48" s="27">
+      <c r="D48" s="60">
         <f>IF(C48&lt;=계산기!$C$22/2,C48,계산기!$C$22*(1-계산기!$C$22/(4*C48)))</f>
         <v/>
       </c>
-      <c r="E48" s="27">
+      <c r="E48" s="60">
         <f>MIN(D48/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2920,22 +4383,22 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="26" t="n">
+      <c r="A49" s="59" t="n">
         <v>0.245</v>
       </c>
-      <c r="B49" s="27">
+      <c r="B49" s="60">
         <f>계산기!$C$7*계산기!$C$8/A49</f>
         <v/>
       </c>
-      <c r="C49" s="27">
+      <c r="C49" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A49/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D49" s="27">
+      <c r="D49" s="60">
         <f>IF(C49&lt;=계산기!$C$22/2,C49,계산기!$C$22*(1-계산기!$C$22/(4*C49)))</f>
         <v/>
       </c>
-      <c r="E49" s="27">
+      <c r="E49" s="60">
         <f>MIN(D49/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2945,22 +4408,22 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="26" t="n">
+      <c r="A50" s="59" t="n">
         <v>0.25</v>
       </c>
-      <c r="B50" s="27">
+      <c r="B50" s="60">
         <f>계산기!$C$7*계산기!$C$8/A50</f>
         <v/>
       </c>
-      <c r="C50" s="27">
+      <c r="C50" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A50/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D50" s="27">
+      <c r="D50" s="60">
         <f>IF(C50&lt;=계산기!$C$22/2,C50,계산기!$C$22*(1-계산기!$C$22/(4*C50)))</f>
         <v/>
       </c>
-      <c r="E50" s="27">
+      <c r="E50" s="60">
         <f>MIN(D50/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2970,22 +4433,22 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="26" t="n">
+      <c r="A51" s="59" t="n">
         <v>0.255</v>
       </c>
-      <c r="B51" s="27">
+      <c r="B51" s="60">
         <f>계산기!$C$7*계산기!$C$8/A51</f>
         <v/>
       </c>
-      <c r="C51" s="27">
+      <c r="C51" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A51/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D51" s="27">
+      <c r="D51" s="60">
         <f>IF(C51&lt;=계산기!$C$22/2,C51,계산기!$C$22*(1-계산기!$C$22/(4*C51)))</f>
         <v/>
       </c>
-      <c r="E51" s="27">
+      <c r="E51" s="60">
         <f>MIN(D51/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -2995,22 +4458,22 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="26" t="n">
+      <c r="A52" s="59" t="n">
         <v>0.26</v>
       </c>
-      <c r="B52" s="27">
+      <c r="B52" s="60">
         <f>계산기!$C$7*계산기!$C$8/A52</f>
         <v/>
       </c>
-      <c r="C52" s="27">
+      <c r="C52" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A52/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D52" s="27">
+      <c r="D52" s="60">
         <f>IF(C52&lt;=계산기!$C$22/2,C52,계산기!$C$22*(1-계산기!$C$22/(4*C52)))</f>
         <v/>
       </c>
-      <c r="E52" s="27">
+      <c r="E52" s="60">
         <f>MIN(D52/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3020,22 +4483,22 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="26" t="n">
+      <c r="A53" s="59" t="n">
         <v>0.265</v>
       </c>
-      <c r="B53" s="27">
+      <c r="B53" s="60">
         <f>계산기!$C$7*계산기!$C$8/A53</f>
         <v/>
       </c>
-      <c r="C53" s="27">
+      <c r="C53" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A53/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D53" s="27">
+      <c r="D53" s="60">
         <f>IF(C53&lt;=계산기!$C$22/2,C53,계산기!$C$22*(1-계산기!$C$22/(4*C53)))</f>
         <v/>
       </c>
-      <c r="E53" s="27">
+      <c r="E53" s="60">
         <f>MIN(D53/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3045,22 +4508,22 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="26" t="n">
+      <c r="A54" s="59" t="n">
         <v>0.27</v>
       </c>
-      <c r="B54" s="27">
+      <c r="B54" s="60">
         <f>계산기!$C$7*계산기!$C$8/A54</f>
         <v/>
       </c>
-      <c r="C54" s="27">
+      <c r="C54" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A54/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D54" s="27">
+      <c r="D54" s="60">
         <f>IF(C54&lt;=계산기!$C$22/2,C54,계산기!$C$22*(1-계산기!$C$22/(4*C54)))</f>
         <v/>
       </c>
-      <c r="E54" s="27">
+      <c r="E54" s="60">
         <f>MIN(D54/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3070,22 +4533,22 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="26" t="n">
+      <c r="A55" s="59" t="n">
         <v>0.275</v>
       </c>
-      <c r="B55" s="27">
+      <c r="B55" s="60">
         <f>계산기!$C$7*계산기!$C$8/A55</f>
         <v/>
       </c>
-      <c r="C55" s="27">
+      <c r="C55" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A55/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D55" s="27">
+      <c r="D55" s="60">
         <f>IF(C55&lt;=계산기!$C$22/2,C55,계산기!$C$22*(1-계산기!$C$22/(4*C55)))</f>
         <v/>
       </c>
-      <c r="E55" s="27">
+      <c r="E55" s="60">
         <f>MIN(D55/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3095,22 +4558,22 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="26" t="n">
+      <c r="A56" s="59" t="n">
         <v>0.28</v>
       </c>
-      <c r="B56" s="27">
+      <c r="B56" s="60">
         <f>계산기!$C$7*계산기!$C$8/A56</f>
         <v/>
       </c>
-      <c r="C56" s="27">
+      <c r="C56" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A56/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D56" s="27">
+      <c r="D56" s="60">
         <f>IF(C56&lt;=계산기!$C$22/2,C56,계산기!$C$22*(1-계산기!$C$22/(4*C56)))</f>
         <v/>
       </c>
-      <c r="E56" s="27">
+      <c r="E56" s="60">
         <f>MIN(D56/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3120,22 +4583,22 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="26" t="n">
+      <c r="A57" s="59" t="n">
         <v>0.285</v>
       </c>
-      <c r="B57" s="27">
+      <c r="B57" s="60">
         <f>계산기!$C$7*계산기!$C$8/A57</f>
         <v/>
       </c>
-      <c r="C57" s="27">
+      <c r="C57" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A57/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D57" s="27">
+      <c r="D57" s="60">
         <f>IF(C57&lt;=계산기!$C$22/2,C57,계산기!$C$22*(1-계산기!$C$22/(4*C57)))</f>
         <v/>
       </c>
-      <c r="E57" s="27">
+      <c r="E57" s="60">
         <f>MIN(D57/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3145,22 +4608,22 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="26" t="n">
+      <c r="A58" s="59" t="n">
         <v>0.29</v>
       </c>
-      <c r="B58" s="27">
+      <c r="B58" s="60">
         <f>계산기!$C$7*계산기!$C$8/A58</f>
         <v/>
       </c>
-      <c r="C58" s="27">
+      <c r="C58" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A58/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D58" s="27">
+      <c r="D58" s="60">
         <f>IF(C58&lt;=계산기!$C$22/2,C58,계산기!$C$22*(1-계산기!$C$22/(4*C58)))</f>
         <v/>
       </c>
-      <c r="E58" s="27">
+      <c r="E58" s="60">
         <f>MIN(D58/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3170,22 +4633,22 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="26" t="n">
+      <c r="A59" s="59" t="n">
         <v>0.295</v>
       </c>
-      <c r="B59" s="27">
+      <c r="B59" s="60">
         <f>계산기!$C$7*계산기!$C$8/A59</f>
         <v/>
       </c>
-      <c r="C59" s="27">
+      <c r="C59" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A59/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D59" s="27">
+      <c r="D59" s="60">
         <f>IF(C59&lt;=계산기!$C$22/2,C59,계산기!$C$22*(1-계산기!$C$22/(4*C59)))</f>
         <v/>
       </c>
-      <c r="E59" s="27">
+      <c r="E59" s="60">
         <f>MIN(D59/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3195,22 +4658,22 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="26" t="n">
+      <c r="A60" s="59" t="n">
         <v>0.3</v>
       </c>
-      <c r="B60" s="27">
+      <c r="B60" s="60">
         <f>계산기!$C$7*계산기!$C$8/A60</f>
         <v/>
       </c>
-      <c r="C60" s="27">
+      <c r="C60" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A60/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D60" s="27">
+      <c r="D60" s="60">
         <f>IF(C60&lt;=계산기!$C$22/2,C60,계산기!$C$22*(1-계산기!$C$22/(4*C60)))</f>
         <v/>
       </c>
-      <c r="E60" s="27">
+      <c r="E60" s="60">
         <f>MIN(D60/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3220,22 +4683,22 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="26" t="n">
+      <c r="A61" s="59" t="n">
         <v>0.305</v>
       </c>
-      <c r="B61" s="27">
+      <c r="B61" s="60">
         <f>계산기!$C$7*계산기!$C$8/A61</f>
         <v/>
       </c>
-      <c r="C61" s="27">
+      <c r="C61" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A61/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D61" s="27">
+      <c r="D61" s="60">
         <f>IF(C61&lt;=계산기!$C$22/2,C61,계산기!$C$22*(1-계산기!$C$22/(4*C61)))</f>
         <v/>
       </c>
-      <c r="E61" s="27">
+      <c r="E61" s="60">
         <f>MIN(D61/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3245,22 +4708,22 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="26" t="n">
+      <c r="A62" s="59" t="n">
         <v>0.31</v>
       </c>
-      <c r="B62" s="27">
+      <c r="B62" s="60">
         <f>계산기!$C$7*계산기!$C$8/A62</f>
         <v/>
       </c>
-      <c r="C62" s="27">
+      <c r="C62" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A62/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D62" s="27">
+      <c r="D62" s="60">
         <f>IF(C62&lt;=계산기!$C$22/2,C62,계산기!$C$22*(1-계산기!$C$22/(4*C62)))</f>
         <v/>
       </c>
-      <c r="E62" s="27">
+      <c r="E62" s="60">
         <f>MIN(D62/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3270,22 +4733,22 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="26" t="n">
+      <c r="A63" s="59" t="n">
         <v>0.315</v>
       </c>
-      <c r="B63" s="27">
+      <c r="B63" s="60">
         <f>계산기!$C$7*계산기!$C$8/A63</f>
         <v/>
       </c>
-      <c r="C63" s="27">
+      <c r="C63" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A63/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D63" s="27">
+      <c r="D63" s="60">
         <f>IF(C63&lt;=계산기!$C$22/2,C63,계산기!$C$22*(1-계산기!$C$22/(4*C63)))</f>
         <v/>
       </c>
-      <c r="E63" s="27">
+      <c r="E63" s="60">
         <f>MIN(D63/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3295,22 +4758,22 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="26" t="n">
+      <c r="A64" s="59" t="n">
         <v>0.32</v>
       </c>
-      <c r="B64" s="27">
+      <c r="B64" s="60">
         <f>계산기!$C$7*계산기!$C$8/A64</f>
         <v/>
       </c>
-      <c r="C64" s="27">
+      <c r="C64" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A64/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D64" s="27">
+      <c r="D64" s="60">
         <f>IF(C64&lt;=계산기!$C$22/2,C64,계산기!$C$22*(1-계산기!$C$22/(4*C64)))</f>
         <v/>
       </c>
-      <c r="E64" s="27">
+      <c r="E64" s="60">
         <f>MIN(D64/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3320,22 +4783,22 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="26" t="n">
+      <c r="A65" s="59" t="n">
         <v>0.325</v>
       </c>
-      <c r="B65" s="27">
+      <c r="B65" s="60">
         <f>계산기!$C$7*계산기!$C$8/A65</f>
         <v/>
       </c>
-      <c r="C65" s="27">
+      <c r="C65" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A65/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D65" s="27">
+      <c r="D65" s="60">
         <f>IF(C65&lt;=계산기!$C$22/2,C65,계산기!$C$22*(1-계산기!$C$22/(4*C65)))</f>
         <v/>
       </c>
-      <c r="E65" s="27">
+      <c r="E65" s="60">
         <f>MIN(D65/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3345,22 +4808,22 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="26" t="n">
+      <c r="A66" s="59" t="n">
         <v>0.33</v>
       </c>
-      <c r="B66" s="27">
+      <c r="B66" s="60">
         <f>계산기!$C$7*계산기!$C$8/A66</f>
         <v/>
       </c>
-      <c r="C66" s="27">
+      <c r="C66" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A66/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D66" s="27">
+      <c r="D66" s="60">
         <f>IF(C66&lt;=계산기!$C$22/2,C66,계산기!$C$22*(1-계산기!$C$22/(4*C66)))</f>
         <v/>
       </c>
-      <c r="E66" s="27">
+      <c r="E66" s="60">
         <f>MIN(D66/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3370,22 +4833,22 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="26" t="n">
+      <c r="A67" s="59" t="n">
         <v>0.335</v>
       </c>
-      <c r="B67" s="27">
+      <c r="B67" s="60">
         <f>계산기!$C$7*계산기!$C$8/A67</f>
         <v/>
       </c>
-      <c r="C67" s="27">
+      <c r="C67" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A67/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D67" s="27">
+      <c r="D67" s="60">
         <f>IF(C67&lt;=계산기!$C$22/2,C67,계산기!$C$22*(1-계산기!$C$22/(4*C67)))</f>
         <v/>
       </c>
-      <c r="E67" s="27">
+      <c r="E67" s="60">
         <f>MIN(D67/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3395,22 +4858,22 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="26" t="n">
+      <c r="A68" s="59" t="n">
         <v>0.34</v>
       </c>
-      <c r="B68" s="27">
+      <c r="B68" s="60">
         <f>계산기!$C$7*계산기!$C$8/A68</f>
         <v/>
       </c>
-      <c r="C68" s="27">
+      <c r="C68" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A68/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D68" s="27">
+      <c r="D68" s="60">
         <f>IF(C68&lt;=계산기!$C$22/2,C68,계산기!$C$22*(1-계산기!$C$22/(4*C68)))</f>
         <v/>
       </c>
-      <c r="E68" s="27">
+      <c r="E68" s="60">
         <f>MIN(D68/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3420,22 +4883,22 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="26" t="n">
+      <c r="A69" s="59" t="n">
         <v>0.345</v>
       </c>
-      <c r="B69" s="27">
+      <c r="B69" s="60">
         <f>계산기!$C$7*계산기!$C$8/A69</f>
         <v/>
       </c>
-      <c r="C69" s="27">
+      <c r="C69" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A69/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D69" s="27">
+      <c r="D69" s="60">
         <f>IF(C69&lt;=계산기!$C$22/2,C69,계산기!$C$22*(1-계산기!$C$22/(4*C69)))</f>
         <v/>
       </c>
-      <c r="E69" s="27">
+      <c r="E69" s="60">
         <f>MIN(D69/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3445,22 +4908,22 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="26" t="n">
+      <c r="A70" s="59" t="n">
         <v>0.35</v>
       </c>
-      <c r="B70" s="27">
+      <c r="B70" s="60">
         <f>계산기!$C$7*계산기!$C$8/A70</f>
         <v/>
       </c>
-      <c r="C70" s="27">
+      <c r="C70" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A70/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D70" s="27">
+      <c r="D70" s="60">
         <f>IF(C70&lt;=계산기!$C$22/2,C70,계산기!$C$22*(1-계산기!$C$22/(4*C70)))</f>
         <v/>
       </c>
-      <c r="E70" s="27">
+      <c r="E70" s="60">
         <f>MIN(D70/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3470,22 +4933,22 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="26" t="n">
+      <c r="A71" s="59" t="n">
         <v>0.355</v>
       </c>
-      <c r="B71" s="27">
+      <c r="B71" s="60">
         <f>계산기!$C$7*계산기!$C$8/A71</f>
         <v/>
       </c>
-      <c r="C71" s="27">
+      <c r="C71" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A71/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D71" s="27">
+      <c r="D71" s="60">
         <f>IF(C71&lt;=계산기!$C$22/2,C71,계산기!$C$22*(1-계산기!$C$22/(4*C71)))</f>
         <v/>
       </c>
-      <c r="E71" s="27">
+      <c r="E71" s="60">
         <f>MIN(D71/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3495,22 +4958,22 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="26" t="n">
+      <c r="A72" s="59" t="n">
         <v>0.36</v>
       </c>
-      <c r="B72" s="27">
+      <c r="B72" s="60">
         <f>계산기!$C$7*계산기!$C$8/A72</f>
         <v/>
       </c>
-      <c r="C72" s="27">
+      <c r="C72" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A72/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D72" s="27">
+      <c r="D72" s="60">
         <f>IF(C72&lt;=계산기!$C$22/2,C72,계산기!$C$22*(1-계산기!$C$22/(4*C72)))</f>
         <v/>
       </c>
-      <c r="E72" s="27">
+      <c r="E72" s="60">
         <f>MIN(D72/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3520,22 +4983,22 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="26" t="n">
+      <c r="A73" s="59" t="n">
         <v>0.365</v>
       </c>
-      <c r="B73" s="27">
+      <c r="B73" s="60">
         <f>계산기!$C$7*계산기!$C$8/A73</f>
         <v/>
       </c>
-      <c r="C73" s="27">
+      <c r="C73" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A73/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D73" s="27">
+      <c r="D73" s="60">
         <f>IF(C73&lt;=계산기!$C$22/2,C73,계산기!$C$22*(1-계산기!$C$22/(4*C73)))</f>
         <v/>
       </c>
-      <c r="E73" s="27">
+      <c r="E73" s="60">
         <f>MIN(D73/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3545,22 +5008,22 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="26" t="n">
+      <c r="A74" s="59" t="n">
         <v>0.37</v>
       </c>
-      <c r="B74" s="27">
+      <c r="B74" s="60">
         <f>계산기!$C$7*계산기!$C$8/A74</f>
         <v/>
       </c>
-      <c r="C74" s="27">
+      <c r="C74" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A74/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D74" s="27">
+      <c r="D74" s="60">
         <f>IF(C74&lt;=계산기!$C$22/2,C74,계산기!$C$22*(1-계산기!$C$22/(4*C74)))</f>
         <v/>
       </c>
-      <c r="E74" s="27">
+      <c r="E74" s="60">
         <f>MIN(D74/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3570,22 +5033,22 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="26" t="n">
+      <c r="A75" s="59" t="n">
         <v>0.375</v>
       </c>
-      <c r="B75" s="27">
+      <c r="B75" s="60">
         <f>계산기!$C$7*계산기!$C$8/A75</f>
         <v/>
       </c>
-      <c r="C75" s="27">
+      <c r="C75" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A75/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D75" s="27">
+      <c r="D75" s="60">
         <f>IF(C75&lt;=계산기!$C$22/2,C75,계산기!$C$22*(1-계산기!$C$22/(4*C75)))</f>
         <v/>
       </c>
-      <c r="E75" s="27">
+      <c r="E75" s="60">
         <f>MIN(D75/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3595,22 +5058,22 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="26" t="n">
+      <c r="A76" s="59" t="n">
         <v>0.38</v>
       </c>
-      <c r="B76" s="27">
+      <c r="B76" s="60">
         <f>계산기!$C$7*계산기!$C$8/A76</f>
         <v/>
       </c>
-      <c r="C76" s="27">
+      <c r="C76" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A76/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D76" s="27">
+      <c r="D76" s="60">
         <f>IF(C76&lt;=계산기!$C$22/2,C76,계산기!$C$22*(1-계산기!$C$22/(4*C76)))</f>
         <v/>
       </c>
-      <c r="E76" s="27">
+      <c r="E76" s="60">
         <f>MIN(D76/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3620,22 +5083,22 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="26" t="n">
+      <c r="A77" s="59" t="n">
         <v>0.385</v>
       </c>
-      <c r="B77" s="27">
+      <c r="B77" s="60">
         <f>계산기!$C$7*계산기!$C$8/A77</f>
         <v/>
       </c>
-      <c r="C77" s="27">
+      <c r="C77" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A77/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D77" s="27">
+      <c r="D77" s="60">
         <f>IF(C77&lt;=계산기!$C$22/2,C77,계산기!$C$22*(1-계산기!$C$22/(4*C77)))</f>
         <v/>
       </c>
-      <c r="E77" s="27">
+      <c r="E77" s="60">
         <f>MIN(D77/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3645,22 +5108,22 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="26" t="n">
+      <c r="A78" s="59" t="n">
         <v>0.39</v>
       </c>
-      <c r="B78" s="27">
+      <c r="B78" s="60">
         <f>계산기!$C$7*계산기!$C$8/A78</f>
         <v/>
       </c>
-      <c r="C78" s="27">
+      <c r="C78" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A78/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D78" s="27">
+      <c r="D78" s="60">
         <f>IF(C78&lt;=계산기!$C$22/2,C78,계산기!$C$22*(1-계산기!$C$22/(4*C78)))</f>
         <v/>
       </c>
-      <c r="E78" s="27">
+      <c r="E78" s="60">
         <f>MIN(D78/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3670,22 +5133,22 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="26" t="n">
+      <c r="A79" s="59" t="n">
         <v>0.395</v>
       </c>
-      <c r="B79" s="27">
+      <c r="B79" s="60">
         <f>계산기!$C$7*계산기!$C$8/A79</f>
         <v/>
       </c>
-      <c r="C79" s="27">
+      <c r="C79" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A79/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D79" s="27">
+      <c r="D79" s="60">
         <f>IF(C79&lt;=계산기!$C$22/2,C79,계산기!$C$22*(1-계산기!$C$22/(4*C79)))</f>
         <v/>
       </c>
-      <c r="E79" s="27">
+      <c r="E79" s="60">
         <f>MIN(D79/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3695,22 +5158,22 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="26" t="n">
+      <c r="A80" s="59" t="n">
         <v>0.4</v>
       </c>
-      <c r="B80" s="27">
+      <c r="B80" s="60">
         <f>계산기!$C$7*계산기!$C$8/A80</f>
         <v/>
       </c>
-      <c r="C80" s="27">
+      <c r="C80" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A80/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D80" s="27">
+      <c r="D80" s="60">
         <f>IF(C80&lt;=계산기!$C$22/2,C80,계산기!$C$22*(1-계산기!$C$22/(4*C80)))</f>
         <v/>
       </c>
-      <c r="E80" s="27">
+      <c r="E80" s="60">
         <f>MIN(D80/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3720,22 +5183,22 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="26" t="n">
+      <c r="A81" s="59" t="n">
         <v>0.405</v>
       </c>
-      <c r="B81" s="27">
+      <c r="B81" s="60">
         <f>계산기!$C$7*계산기!$C$8/A81</f>
         <v/>
       </c>
-      <c r="C81" s="27">
+      <c r="C81" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A81/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D81" s="27">
+      <c r="D81" s="60">
         <f>IF(C81&lt;=계산기!$C$22/2,C81,계산기!$C$22*(1-계산기!$C$22/(4*C81)))</f>
         <v/>
       </c>
-      <c r="E81" s="27">
+      <c r="E81" s="60">
         <f>MIN(D81/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3745,22 +5208,22 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="26" t="n">
+      <c r="A82" s="59" t="n">
         <v>0.41</v>
       </c>
-      <c r="B82" s="27">
+      <c r="B82" s="60">
         <f>계산기!$C$7*계산기!$C$8/A82</f>
         <v/>
       </c>
-      <c r="C82" s="27">
+      <c r="C82" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A82/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D82" s="27">
+      <c r="D82" s="60">
         <f>IF(C82&lt;=계산기!$C$22/2,C82,계산기!$C$22*(1-계산기!$C$22/(4*C82)))</f>
         <v/>
       </c>
-      <c r="E82" s="27">
+      <c r="E82" s="60">
         <f>MIN(D82/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3770,22 +5233,22 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="26" t="n">
+      <c r="A83" s="59" t="n">
         <v>0.415</v>
       </c>
-      <c r="B83" s="27">
+      <c r="B83" s="60">
         <f>계산기!$C$7*계산기!$C$8/A83</f>
         <v/>
       </c>
-      <c r="C83" s="27">
+      <c r="C83" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A83/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D83" s="27">
+      <c r="D83" s="60">
         <f>IF(C83&lt;=계산기!$C$22/2,C83,계산기!$C$22*(1-계산기!$C$22/(4*C83)))</f>
         <v/>
       </c>
-      <c r="E83" s="27">
+      <c r="E83" s="60">
         <f>MIN(D83/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3795,22 +5258,22 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="26" t="n">
+      <c r="A84" s="59" t="n">
         <v>0.42</v>
       </c>
-      <c r="B84" s="27">
+      <c r="B84" s="60">
         <f>계산기!$C$7*계산기!$C$8/A84</f>
         <v/>
       </c>
-      <c r="C84" s="27">
+      <c r="C84" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A84/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D84" s="27">
+      <c r="D84" s="60">
         <f>IF(C84&lt;=계산기!$C$22/2,C84,계산기!$C$22*(1-계산기!$C$22/(4*C84)))</f>
         <v/>
       </c>
-      <c r="E84" s="27">
+      <c r="E84" s="60">
         <f>MIN(D84/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3820,22 +5283,22 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="26" t="n">
+      <c r="A85" s="59" t="n">
         <v>0.425</v>
       </c>
-      <c r="B85" s="27">
+      <c r="B85" s="60">
         <f>계산기!$C$7*계산기!$C$8/A85</f>
         <v/>
       </c>
-      <c r="C85" s="27">
+      <c r="C85" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A85/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D85" s="27">
+      <c r="D85" s="60">
         <f>IF(C85&lt;=계산기!$C$22/2,C85,계산기!$C$22*(1-계산기!$C$22/(4*C85)))</f>
         <v/>
       </c>
-      <c r="E85" s="27">
+      <c r="E85" s="60">
         <f>MIN(D85/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3845,22 +5308,22 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="26" t="n">
+      <c r="A86" s="59" t="n">
         <v>0.43</v>
       </c>
-      <c r="B86" s="27">
+      <c r="B86" s="60">
         <f>계산기!$C$7*계산기!$C$8/A86</f>
         <v/>
       </c>
-      <c r="C86" s="27">
+      <c r="C86" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A86/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D86" s="27">
+      <c r="D86" s="60">
         <f>IF(C86&lt;=계산기!$C$22/2,C86,계산기!$C$22*(1-계산기!$C$22/(4*C86)))</f>
         <v/>
       </c>
-      <c r="E86" s="27">
+      <c r="E86" s="60">
         <f>MIN(D86/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3870,22 +5333,22 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="26" t="n">
+      <c r="A87" s="59" t="n">
         <v>0.435</v>
       </c>
-      <c r="B87" s="27">
+      <c r="B87" s="60">
         <f>계산기!$C$7*계산기!$C$8/A87</f>
         <v/>
       </c>
-      <c r="C87" s="27">
+      <c r="C87" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A87/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D87" s="27">
+      <c r="D87" s="60">
         <f>IF(C87&lt;=계산기!$C$22/2,C87,계산기!$C$22*(1-계산기!$C$22/(4*C87)))</f>
         <v/>
       </c>
-      <c r="E87" s="27">
+      <c r="E87" s="60">
         <f>MIN(D87/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3895,22 +5358,22 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="26" t="n">
+      <c r="A88" s="59" t="n">
         <v>0.44</v>
       </c>
-      <c r="B88" s="27">
+      <c r="B88" s="60">
         <f>계산기!$C$7*계산기!$C$8/A88</f>
         <v/>
       </c>
-      <c r="C88" s="27">
+      <c r="C88" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A88/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D88" s="27">
+      <c r="D88" s="60">
         <f>IF(C88&lt;=계산기!$C$22/2,C88,계산기!$C$22*(1-계산기!$C$22/(4*C88)))</f>
         <v/>
       </c>
-      <c r="E88" s="27">
+      <c r="E88" s="60">
         <f>MIN(D88/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3920,22 +5383,22 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="26" t="n">
+      <c r="A89" s="59" t="n">
         <v>0.445</v>
       </c>
-      <c r="B89" s="27">
+      <c r="B89" s="60">
         <f>계산기!$C$7*계산기!$C$8/A89</f>
         <v/>
       </c>
-      <c r="C89" s="27">
+      <c r="C89" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A89/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D89" s="27">
+      <c r="D89" s="60">
         <f>IF(C89&lt;=계산기!$C$22/2,C89,계산기!$C$22*(1-계산기!$C$22/(4*C89)))</f>
         <v/>
       </c>
-      <c r="E89" s="27">
+      <c r="E89" s="60">
         <f>MIN(D89/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3945,22 +5408,22 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="26" t="n">
+      <c r="A90" s="59" t="n">
         <v>0.45</v>
       </c>
-      <c r="B90" s="27">
+      <c r="B90" s="60">
         <f>계산기!$C$7*계산기!$C$8/A90</f>
         <v/>
       </c>
-      <c r="C90" s="27">
+      <c r="C90" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A90/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D90" s="27">
+      <c r="D90" s="60">
         <f>IF(C90&lt;=계산기!$C$22/2,C90,계산기!$C$22*(1-계산기!$C$22/(4*C90)))</f>
         <v/>
       </c>
-      <c r="E90" s="27">
+      <c r="E90" s="60">
         <f>MIN(D90/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3970,22 +5433,22 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="26" t="n">
+      <c r="A91" s="59" t="n">
         <v>0.455</v>
       </c>
-      <c r="B91" s="27">
+      <c r="B91" s="60">
         <f>계산기!$C$7*계산기!$C$8/A91</f>
         <v/>
       </c>
-      <c r="C91" s="27">
+      <c r="C91" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A91/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D91" s="27">
+      <c r="D91" s="60">
         <f>IF(C91&lt;=계산기!$C$22/2,C91,계산기!$C$22*(1-계산기!$C$22/(4*C91)))</f>
         <v/>
       </c>
-      <c r="E91" s="27">
+      <c r="E91" s="60">
         <f>MIN(D91/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -3995,22 +5458,22 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="26" t="n">
+      <c r="A92" s="59" t="n">
         <v>0.46</v>
       </c>
-      <c r="B92" s="27">
+      <c r="B92" s="60">
         <f>계산기!$C$7*계산기!$C$8/A92</f>
         <v/>
       </c>
-      <c r="C92" s="27">
+      <c r="C92" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A92/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D92" s="27">
+      <c r="D92" s="60">
         <f>IF(C92&lt;=계산기!$C$22/2,C92,계산기!$C$22*(1-계산기!$C$22/(4*C92)))</f>
         <v/>
       </c>
-      <c r="E92" s="27">
+      <c r="E92" s="60">
         <f>MIN(D92/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4020,22 +5483,22 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="26" t="n">
+      <c r="A93" s="59" t="n">
         <v>0.465</v>
       </c>
-      <c r="B93" s="27">
+      <c r="B93" s="60">
         <f>계산기!$C$7*계산기!$C$8/A93</f>
         <v/>
       </c>
-      <c r="C93" s="27">
+      <c r="C93" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A93/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D93" s="27">
+      <c r="D93" s="60">
         <f>IF(C93&lt;=계산기!$C$22/2,C93,계산기!$C$22*(1-계산기!$C$22/(4*C93)))</f>
         <v/>
       </c>
-      <c r="E93" s="27">
+      <c r="E93" s="60">
         <f>MIN(D93/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4045,22 +5508,22 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="26" t="n">
+      <c r="A94" s="59" t="n">
         <v>0.47</v>
       </c>
-      <c r="B94" s="27">
+      <c r="B94" s="60">
         <f>계산기!$C$7*계산기!$C$8/A94</f>
         <v/>
       </c>
-      <c r="C94" s="27">
+      <c r="C94" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A94/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D94" s="27">
+      <c r="D94" s="60">
         <f>IF(C94&lt;=계산기!$C$22/2,C94,계산기!$C$22*(1-계산기!$C$22/(4*C94)))</f>
         <v/>
       </c>
-      <c r="E94" s="27">
+      <c r="E94" s="60">
         <f>MIN(D94/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4070,22 +5533,22 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="26" t="n">
+      <c r="A95" s="59" t="n">
         <v>0.475</v>
       </c>
-      <c r="B95" s="27">
+      <c r="B95" s="60">
         <f>계산기!$C$7*계산기!$C$8/A95</f>
         <v/>
       </c>
-      <c r="C95" s="27">
+      <c r="C95" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A95/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D95" s="27">
+      <c r="D95" s="60">
         <f>IF(C95&lt;=계산기!$C$22/2,C95,계산기!$C$22*(1-계산기!$C$22/(4*C95)))</f>
         <v/>
       </c>
-      <c r="E95" s="27">
+      <c r="E95" s="60">
         <f>MIN(D95/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4095,22 +5558,22 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="26" t="n">
+      <c r="A96" s="59" t="n">
         <v>0.48</v>
       </c>
-      <c r="B96" s="27">
+      <c r="B96" s="60">
         <f>계산기!$C$7*계산기!$C$8/A96</f>
         <v/>
       </c>
-      <c r="C96" s="27">
+      <c r="C96" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A96/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D96" s="27">
+      <c r="D96" s="60">
         <f>IF(C96&lt;=계산기!$C$22/2,C96,계산기!$C$22*(1-계산기!$C$22/(4*C96)))</f>
         <v/>
       </c>
-      <c r="E96" s="27">
+      <c r="E96" s="60">
         <f>MIN(D96/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4120,22 +5583,22 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="26" t="n">
+      <c r="A97" s="59" t="n">
         <v>0.485</v>
       </c>
-      <c r="B97" s="27">
+      <c r="B97" s="60">
         <f>계산기!$C$7*계산기!$C$8/A97</f>
         <v/>
       </c>
-      <c r="C97" s="27">
+      <c r="C97" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A97/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D97" s="27">
+      <c r="D97" s="60">
         <f>IF(C97&lt;=계산기!$C$22/2,C97,계산기!$C$22*(1-계산기!$C$22/(4*C97)))</f>
         <v/>
       </c>
-      <c r="E97" s="27">
+      <c r="E97" s="60">
         <f>MIN(D97/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4145,22 +5608,22 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="26" t="n">
+      <c r="A98" s="59" t="n">
         <v>0.49</v>
       </c>
-      <c r="B98" s="27">
+      <c r="B98" s="60">
         <f>계산기!$C$7*계산기!$C$8/A98</f>
         <v/>
       </c>
-      <c r="C98" s="27">
+      <c r="C98" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A98/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D98" s="27">
+      <c r="D98" s="60">
         <f>IF(C98&lt;=계산기!$C$22/2,C98,계산기!$C$22*(1-계산기!$C$22/(4*C98)))</f>
         <v/>
       </c>
-      <c r="E98" s="27">
+      <c r="E98" s="60">
         <f>MIN(D98/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4170,22 +5633,22 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="26" t="n">
+      <c r="A99" s="59" t="n">
         <v>0.495</v>
       </c>
-      <c r="B99" s="27">
+      <c r="B99" s="60">
         <f>계산기!$C$7*계산기!$C$8/A99</f>
         <v/>
       </c>
-      <c r="C99" s="27">
+      <c r="C99" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A99/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D99" s="27">
+      <c r="D99" s="60">
         <f>IF(C99&lt;=계산기!$C$22/2,C99,계산기!$C$22*(1-계산기!$C$22/(4*C99)))</f>
         <v/>
       </c>
-      <c r="E99" s="27">
+      <c r="E99" s="60">
         <f>MIN(D99/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4195,22 +5658,22 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="26" t="n">
+      <c r="A100" s="59" t="n">
         <v>0.5</v>
       </c>
-      <c r="B100" s="27">
+      <c r="B100" s="60">
         <f>계산기!$C$7*계산기!$C$8/A100</f>
         <v/>
       </c>
-      <c r="C100" s="27">
+      <c r="C100" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A100/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D100" s="27">
+      <c r="D100" s="60">
         <f>IF(C100&lt;=계산기!$C$22/2,C100,계산기!$C$22*(1-계산기!$C$22/(4*C100)))</f>
         <v/>
       </c>
-      <c r="E100" s="27">
+      <c r="E100" s="60">
         <f>MIN(D100/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4220,22 +5683,22 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="26" t="n">
+      <c r="A101" s="59" t="n">
         <v>0.505</v>
       </c>
-      <c r="B101" s="27">
+      <c r="B101" s="60">
         <f>계산기!$C$7*계산기!$C$8/A101</f>
         <v/>
       </c>
-      <c r="C101" s="27">
+      <c r="C101" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A101/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D101" s="27">
+      <c r="D101" s="60">
         <f>IF(C101&lt;=계산기!$C$22/2,C101,계산기!$C$22*(1-계산기!$C$22/(4*C101)))</f>
         <v/>
       </c>
-      <c r="E101" s="27">
+      <c r="E101" s="60">
         <f>MIN(D101/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4245,22 +5708,22 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="26" t="n">
+      <c r="A102" s="59" t="n">
         <v>0.51</v>
       </c>
-      <c r="B102" s="27">
+      <c r="B102" s="60">
         <f>계산기!$C$7*계산기!$C$8/A102</f>
         <v/>
       </c>
-      <c r="C102" s="27">
+      <c r="C102" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A102/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D102" s="27">
+      <c r="D102" s="60">
         <f>IF(C102&lt;=계산기!$C$22/2,C102,계산기!$C$22*(1-계산기!$C$22/(4*C102)))</f>
         <v/>
       </c>
-      <c r="E102" s="27">
+      <c r="E102" s="60">
         <f>MIN(D102/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4270,22 +5733,22 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="26" t="n">
+      <c r="A103" s="59" t="n">
         <v>0.515</v>
       </c>
-      <c r="B103" s="27">
+      <c r="B103" s="60">
         <f>계산기!$C$7*계산기!$C$8/A103</f>
         <v/>
       </c>
-      <c r="C103" s="27">
+      <c r="C103" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A103/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D103" s="27">
+      <c r="D103" s="60">
         <f>IF(C103&lt;=계산기!$C$22/2,C103,계산기!$C$22*(1-계산기!$C$22/(4*C103)))</f>
         <v/>
       </c>
-      <c r="E103" s="27">
+      <c r="E103" s="60">
         <f>MIN(D103/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4295,22 +5758,22 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="26" t="n">
+      <c r="A104" s="59" t="n">
         <v>0.52</v>
       </c>
-      <c r="B104" s="27">
+      <c r="B104" s="60">
         <f>계산기!$C$7*계산기!$C$8/A104</f>
         <v/>
       </c>
-      <c r="C104" s="27">
+      <c r="C104" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A104/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D104" s="27">
+      <c r="D104" s="60">
         <f>IF(C104&lt;=계산기!$C$22/2,C104,계산기!$C$22*(1-계산기!$C$22/(4*C104)))</f>
         <v/>
       </c>
-      <c r="E104" s="27">
+      <c r="E104" s="60">
         <f>MIN(D104/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4320,22 +5783,22 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="26" t="n">
+      <c r="A105" s="59" t="n">
         <v>0.525</v>
       </c>
-      <c r="B105" s="27">
+      <c r="B105" s="60">
         <f>계산기!$C$7*계산기!$C$8/A105</f>
         <v/>
       </c>
-      <c r="C105" s="27">
+      <c r="C105" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A105/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D105" s="27">
+      <c r="D105" s="60">
         <f>IF(C105&lt;=계산기!$C$22/2,C105,계산기!$C$22*(1-계산기!$C$22/(4*C105)))</f>
         <v/>
       </c>
-      <c r="E105" s="27">
+      <c r="E105" s="60">
         <f>MIN(D105/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4345,22 +5808,22 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="26" t="n">
+      <c r="A106" s="59" t="n">
         <v>0.53</v>
       </c>
-      <c r="B106" s="27">
+      <c r="B106" s="60">
         <f>계산기!$C$7*계산기!$C$8/A106</f>
         <v/>
       </c>
-      <c r="C106" s="27">
+      <c r="C106" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A106/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D106" s="27">
+      <c r="D106" s="60">
         <f>IF(C106&lt;=계산기!$C$22/2,C106,계산기!$C$22*(1-계산기!$C$22/(4*C106)))</f>
         <v/>
       </c>
-      <c r="E106" s="27">
+      <c r="E106" s="60">
         <f>MIN(D106/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4370,22 +5833,22 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="26" t="n">
+      <c r="A107" s="59" t="n">
         <v>0.535</v>
       </c>
-      <c r="B107" s="27">
+      <c r="B107" s="60">
         <f>계산기!$C$7*계산기!$C$8/A107</f>
         <v/>
       </c>
-      <c r="C107" s="27">
+      <c r="C107" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A107/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D107" s="27">
+      <c r="D107" s="60">
         <f>IF(C107&lt;=계산기!$C$22/2,C107,계산기!$C$22*(1-계산기!$C$22/(4*C107)))</f>
         <v/>
       </c>
-      <c r="E107" s="27">
+      <c r="E107" s="60">
         <f>MIN(D107/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4395,22 +5858,22 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="26" t="n">
+      <c r="A108" s="59" t="n">
         <v>0.54</v>
       </c>
-      <c r="B108" s="27">
+      <c r="B108" s="60">
         <f>계산기!$C$7*계산기!$C$8/A108</f>
         <v/>
       </c>
-      <c r="C108" s="27">
+      <c r="C108" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A108/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D108" s="27">
+      <c r="D108" s="60">
         <f>IF(C108&lt;=계산기!$C$22/2,C108,계산기!$C$22*(1-계산기!$C$22/(4*C108)))</f>
         <v/>
       </c>
-      <c r="E108" s="27">
+      <c r="E108" s="60">
         <f>MIN(D108/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4420,22 +5883,22 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="26" t="n">
+      <c r="A109" s="59" t="n">
         <v>0.545</v>
       </c>
-      <c r="B109" s="27">
+      <c r="B109" s="60">
         <f>계산기!$C$7*계산기!$C$8/A109</f>
         <v/>
       </c>
-      <c r="C109" s="27">
+      <c r="C109" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A109/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D109" s="27">
+      <c r="D109" s="60">
         <f>IF(C109&lt;=계산기!$C$22/2,C109,계산기!$C$22*(1-계산기!$C$22/(4*C109)))</f>
         <v/>
       </c>
-      <c r="E109" s="27">
+      <c r="E109" s="60">
         <f>MIN(D109/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4445,22 +5908,22 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="26" t="n">
+      <c r="A110" s="59" t="n">
         <v>0.55</v>
       </c>
-      <c r="B110" s="27">
+      <c r="B110" s="60">
         <f>계산기!$C$7*계산기!$C$8/A110</f>
         <v/>
       </c>
-      <c r="C110" s="27">
+      <c r="C110" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A110/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D110" s="27">
+      <c r="D110" s="60">
         <f>IF(C110&lt;=계산기!$C$22/2,C110,계산기!$C$22*(1-계산기!$C$22/(4*C110)))</f>
         <v/>
       </c>
-      <c r="E110" s="27">
+      <c r="E110" s="60">
         <f>MIN(D110/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4470,22 +5933,22 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="26" t="n">
+      <c r="A111" s="59" t="n">
         <v>0.555</v>
       </c>
-      <c r="B111" s="27">
+      <c r="B111" s="60">
         <f>계산기!$C$7*계산기!$C$8/A111</f>
         <v/>
       </c>
-      <c r="C111" s="27">
+      <c r="C111" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A111/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D111" s="27">
+      <c r="D111" s="60">
         <f>IF(C111&lt;=계산기!$C$22/2,C111,계산기!$C$22*(1-계산기!$C$22/(4*C111)))</f>
         <v/>
       </c>
-      <c r="E111" s="27">
+      <c r="E111" s="60">
         <f>MIN(D111/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4495,22 +5958,22 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="26" t="n">
+      <c r="A112" s="59" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="B112" s="27">
+      <c r="B112" s="60">
         <f>계산기!$C$7*계산기!$C$8/A112</f>
         <v/>
       </c>
-      <c r="C112" s="27">
+      <c r="C112" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A112/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D112" s="27">
+      <c r="D112" s="60">
         <f>IF(C112&lt;=계산기!$C$22/2,C112,계산기!$C$22*(1-계산기!$C$22/(4*C112)))</f>
         <v/>
       </c>
-      <c r="E112" s="27">
+      <c r="E112" s="60">
         <f>MIN(D112/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4520,22 +5983,22 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="26" t="n">
+      <c r="A113" s="59" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="B113" s="27">
+      <c r="B113" s="60">
         <f>계산기!$C$7*계산기!$C$8/A113</f>
         <v/>
       </c>
-      <c r="C113" s="27">
+      <c r="C113" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A113/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D113" s="27">
+      <c r="D113" s="60">
         <f>IF(C113&lt;=계산기!$C$22/2,C113,계산기!$C$22*(1-계산기!$C$22/(4*C113)))</f>
         <v/>
       </c>
-      <c r="E113" s="27">
+      <c r="E113" s="60">
         <f>MIN(D113/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4545,22 +6008,22 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="26" t="n">
+      <c r="A114" s="59" t="n">
         <v>0.57</v>
       </c>
-      <c r="B114" s="27">
+      <c r="B114" s="60">
         <f>계산기!$C$7*계산기!$C$8/A114</f>
         <v/>
       </c>
-      <c r="C114" s="27">
+      <c r="C114" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A114/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D114" s="27">
+      <c r="D114" s="60">
         <f>IF(C114&lt;=계산기!$C$22/2,C114,계산기!$C$22*(1-계산기!$C$22/(4*C114)))</f>
         <v/>
       </c>
-      <c r="E114" s="27">
+      <c r="E114" s="60">
         <f>MIN(D114/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4570,22 +6033,22 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="26" t="n">
+      <c r="A115" s="59" t="n">
         <v>0.575</v>
       </c>
-      <c r="B115" s="27">
+      <c r="B115" s="60">
         <f>계산기!$C$7*계산기!$C$8/A115</f>
         <v/>
       </c>
-      <c r="C115" s="27">
+      <c r="C115" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A115/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D115" s="27">
+      <c r="D115" s="60">
         <f>IF(C115&lt;=계산기!$C$22/2,C115,계산기!$C$22*(1-계산기!$C$22/(4*C115)))</f>
         <v/>
       </c>
-      <c r="E115" s="27">
+      <c r="E115" s="60">
         <f>MIN(D115/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4595,22 +6058,22 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="26" t="n">
+      <c r="A116" s="59" t="n">
         <v>0.58</v>
       </c>
-      <c r="B116" s="27">
+      <c r="B116" s="60">
         <f>계산기!$C$7*계산기!$C$8/A116</f>
         <v/>
       </c>
-      <c r="C116" s="27">
+      <c r="C116" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A116/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D116" s="27">
+      <c r="D116" s="60">
         <f>IF(C116&lt;=계산기!$C$22/2,C116,계산기!$C$22*(1-계산기!$C$22/(4*C116)))</f>
         <v/>
       </c>
-      <c r="E116" s="27">
+      <c r="E116" s="60">
         <f>MIN(D116/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4620,22 +6083,22 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="26" t="n">
+      <c r="A117" s="59" t="n">
         <v>0.585</v>
       </c>
-      <c r="B117" s="27">
+      <c r="B117" s="60">
         <f>계산기!$C$7*계산기!$C$8/A117</f>
         <v/>
       </c>
-      <c r="C117" s="27">
+      <c r="C117" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A117/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D117" s="27">
+      <c r="D117" s="60">
         <f>IF(C117&lt;=계산기!$C$22/2,C117,계산기!$C$22*(1-계산기!$C$22/(4*C117)))</f>
         <v/>
       </c>
-      <c r="E117" s="27">
+      <c r="E117" s="60">
         <f>MIN(D117/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4645,22 +6108,22 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="26" t="n">
+      <c r="A118" s="59" t="n">
         <v>0.59</v>
       </c>
-      <c r="B118" s="27">
+      <c r="B118" s="60">
         <f>계산기!$C$7*계산기!$C$8/A118</f>
         <v/>
       </c>
-      <c r="C118" s="27">
+      <c r="C118" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A118/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D118" s="27">
+      <c r="D118" s="60">
         <f>IF(C118&lt;=계산기!$C$22/2,C118,계산기!$C$22*(1-계산기!$C$22/(4*C118)))</f>
         <v/>
       </c>
-      <c r="E118" s="27">
+      <c r="E118" s="60">
         <f>MIN(D118/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4670,22 +6133,22 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="26" t="n">
+      <c r="A119" s="59" t="n">
         <v>0.595</v>
       </c>
-      <c r="B119" s="27">
+      <c r="B119" s="60">
         <f>계산기!$C$7*계산기!$C$8/A119</f>
         <v/>
       </c>
-      <c r="C119" s="27">
+      <c r="C119" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A119/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D119" s="27">
+      <c r="D119" s="60">
         <f>IF(C119&lt;=계산기!$C$22/2,C119,계산기!$C$22*(1-계산기!$C$22/(4*C119)))</f>
         <v/>
       </c>
-      <c r="E119" s="27">
+      <c r="E119" s="60">
         <f>MIN(D119/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4695,22 +6158,22 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="26" t="n">
+      <c r="A120" s="59" t="n">
         <v>0.6</v>
       </c>
-      <c r="B120" s="27">
+      <c r="B120" s="60">
         <f>계산기!$C$7*계산기!$C$8/A120</f>
         <v/>
       </c>
-      <c r="C120" s="27">
+      <c r="C120" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A120/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D120" s="27">
+      <c r="D120" s="60">
         <f>IF(C120&lt;=계산기!$C$22/2,C120,계산기!$C$22*(1-계산기!$C$22/(4*C120)))</f>
         <v/>
       </c>
-      <c r="E120" s="27">
+      <c r="E120" s="60">
         <f>MIN(D120/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4720,22 +6183,22 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="26" t="n">
+      <c r="A121" s="59" t="n">
         <v>0.605</v>
       </c>
-      <c r="B121" s="27">
+      <c r="B121" s="60">
         <f>계산기!$C$7*계산기!$C$8/A121</f>
         <v/>
       </c>
-      <c r="C121" s="27">
+      <c r="C121" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A121/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D121" s="27">
+      <c r="D121" s="60">
         <f>IF(C121&lt;=계산기!$C$22/2,C121,계산기!$C$22*(1-계산기!$C$22/(4*C121)))</f>
         <v/>
       </c>
-      <c r="E121" s="27">
+      <c r="E121" s="60">
         <f>MIN(D121/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4745,22 +6208,22 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="26" t="n">
+      <c r="A122" s="59" t="n">
         <v>0.61</v>
       </c>
-      <c r="B122" s="27">
+      <c r="B122" s="60">
         <f>계산기!$C$7*계산기!$C$8/A122</f>
         <v/>
       </c>
-      <c r="C122" s="27">
+      <c r="C122" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A122/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D122" s="27">
+      <c r="D122" s="60">
         <f>IF(C122&lt;=계산기!$C$22/2,C122,계산기!$C$22*(1-계산기!$C$22/(4*C122)))</f>
         <v/>
       </c>
-      <c r="E122" s="27">
+      <c r="E122" s="60">
         <f>MIN(D122/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4770,22 +6233,22 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="26" t="n">
+      <c r="A123" s="59" t="n">
         <v>0.615</v>
       </c>
-      <c r="B123" s="27">
+      <c r="B123" s="60">
         <f>계산기!$C$7*계산기!$C$8/A123</f>
         <v/>
       </c>
-      <c r="C123" s="27">
+      <c r="C123" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A123/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D123" s="27">
+      <c r="D123" s="60">
         <f>IF(C123&lt;=계산기!$C$22/2,C123,계산기!$C$22*(1-계산기!$C$22/(4*C123)))</f>
         <v/>
       </c>
-      <c r="E123" s="27">
+      <c r="E123" s="60">
         <f>MIN(D123/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4795,22 +6258,22 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="26" t="n">
+      <c r="A124" s="59" t="n">
         <v>0.62</v>
       </c>
-      <c r="B124" s="27">
+      <c r="B124" s="60">
         <f>계산기!$C$7*계산기!$C$8/A124</f>
         <v/>
       </c>
-      <c r="C124" s="27">
+      <c r="C124" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A124/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D124" s="27">
+      <c r="D124" s="60">
         <f>IF(C124&lt;=계산기!$C$22/2,C124,계산기!$C$22*(1-계산기!$C$22/(4*C124)))</f>
         <v/>
       </c>
-      <c r="E124" s="27">
+      <c r="E124" s="60">
         <f>MIN(D124/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4820,22 +6283,22 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="26" t="n">
+      <c r="A125" s="59" t="n">
         <v>0.625</v>
       </c>
-      <c r="B125" s="27">
+      <c r="B125" s="60">
         <f>계산기!$C$7*계산기!$C$8/A125</f>
         <v/>
       </c>
-      <c r="C125" s="27">
+      <c r="C125" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A125/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D125" s="27">
+      <c r="D125" s="60">
         <f>IF(C125&lt;=계산기!$C$22/2,C125,계산기!$C$22*(1-계산기!$C$22/(4*C125)))</f>
         <v/>
       </c>
-      <c r="E125" s="27">
+      <c r="E125" s="60">
         <f>MIN(D125/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4845,22 +6308,22 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="26" t="n">
+      <c r="A126" s="59" t="n">
         <v>0.63</v>
       </c>
-      <c r="B126" s="27">
+      <c r="B126" s="60">
         <f>계산기!$C$7*계산기!$C$8/A126</f>
         <v/>
       </c>
-      <c r="C126" s="27">
+      <c r="C126" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A126/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D126" s="27">
+      <c r="D126" s="60">
         <f>IF(C126&lt;=계산기!$C$22/2,C126,계산기!$C$22*(1-계산기!$C$22/(4*C126)))</f>
         <v/>
       </c>
-      <c r="E126" s="27">
+      <c r="E126" s="60">
         <f>MIN(D126/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4870,22 +6333,22 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="26" t="n">
+      <c r="A127" s="59" t="n">
         <v>0.635</v>
       </c>
-      <c r="B127" s="27">
+      <c r="B127" s="60">
         <f>계산기!$C$7*계산기!$C$8/A127</f>
         <v/>
       </c>
-      <c r="C127" s="27">
+      <c r="C127" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A127/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D127" s="27">
+      <c r="D127" s="60">
         <f>IF(C127&lt;=계산기!$C$22/2,C127,계산기!$C$22*(1-계산기!$C$22/(4*C127)))</f>
         <v/>
       </c>
-      <c r="E127" s="27">
+      <c r="E127" s="60">
         <f>MIN(D127/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4895,22 +6358,22 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="26" t="n">
+      <c r="A128" s="59" t="n">
         <v>0.64</v>
       </c>
-      <c r="B128" s="27">
+      <c r="B128" s="60">
         <f>계산기!$C$7*계산기!$C$8/A128</f>
         <v/>
       </c>
-      <c r="C128" s="27">
+      <c r="C128" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A128/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D128" s="27">
+      <c r="D128" s="60">
         <f>IF(C128&lt;=계산기!$C$22/2,C128,계산기!$C$22*(1-계산기!$C$22/(4*C128)))</f>
         <v/>
       </c>
-      <c r="E128" s="27">
+      <c r="E128" s="60">
         <f>MIN(D128/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4920,22 +6383,22 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="26" t="n">
+      <c r="A129" s="59" t="n">
         <v>0.645</v>
       </c>
-      <c r="B129" s="27">
+      <c r="B129" s="60">
         <f>계산기!$C$7*계산기!$C$8/A129</f>
         <v/>
       </c>
-      <c r="C129" s="27">
+      <c r="C129" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A129/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D129" s="27">
+      <c r="D129" s="60">
         <f>IF(C129&lt;=계산기!$C$22/2,C129,계산기!$C$22*(1-계산기!$C$22/(4*C129)))</f>
         <v/>
       </c>
-      <c r="E129" s="27">
+      <c r="E129" s="60">
         <f>MIN(D129/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4945,22 +6408,22 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="26" t="n">
+      <c r="A130" s="59" t="n">
         <v>0.65</v>
       </c>
-      <c r="B130" s="27">
+      <c r="B130" s="60">
         <f>계산기!$C$7*계산기!$C$8/A130</f>
         <v/>
       </c>
-      <c r="C130" s="27">
+      <c r="C130" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A130/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D130" s="27">
+      <c r="D130" s="60">
         <f>IF(C130&lt;=계산기!$C$22/2,C130,계산기!$C$22*(1-계산기!$C$22/(4*C130)))</f>
         <v/>
       </c>
-      <c r="E130" s="27">
+      <c r="E130" s="60">
         <f>MIN(D130/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4970,22 +6433,22 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="26" t="n">
+      <c r="A131" s="59" t="n">
         <v>0.655</v>
       </c>
-      <c r="B131" s="27">
+      <c r="B131" s="60">
         <f>계산기!$C$7*계산기!$C$8/A131</f>
         <v/>
       </c>
-      <c r="C131" s="27">
+      <c r="C131" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A131/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D131" s="27">
+      <c r="D131" s="60">
         <f>IF(C131&lt;=계산기!$C$22/2,C131,계산기!$C$22*(1-계산기!$C$22/(4*C131)))</f>
         <v/>
       </c>
-      <c r="E131" s="27">
+      <c r="E131" s="60">
         <f>MIN(D131/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -4995,22 +6458,22 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="26" t="n">
+      <c r="A132" s="59" t="n">
         <v>0.66</v>
       </c>
-      <c r="B132" s="27">
+      <c r="B132" s="60">
         <f>계산기!$C$7*계산기!$C$8/A132</f>
         <v/>
       </c>
-      <c r="C132" s="27">
+      <c r="C132" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A132/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D132" s="27">
+      <c r="D132" s="60">
         <f>IF(C132&lt;=계산기!$C$22/2,C132,계산기!$C$22*(1-계산기!$C$22/(4*C132)))</f>
         <v/>
       </c>
-      <c r="E132" s="27">
+      <c r="E132" s="60">
         <f>MIN(D132/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5020,22 +6483,22 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="26" t="n">
+      <c r="A133" s="59" t="n">
         <v>0.665</v>
       </c>
-      <c r="B133" s="27">
+      <c r="B133" s="60">
         <f>계산기!$C$7*계산기!$C$8/A133</f>
         <v/>
       </c>
-      <c r="C133" s="27">
+      <c r="C133" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A133/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D133" s="27">
+      <c r="D133" s="60">
         <f>IF(C133&lt;=계산기!$C$22/2,C133,계산기!$C$22*(1-계산기!$C$22/(4*C133)))</f>
         <v/>
       </c>
-      <c r="E133" s="27">
+      <c r="E133" s="60">
         <f>MIN(D133/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5045,22 +6508,22 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="26" t="n">
+      <c r="A134" s="59" t="n">
         <v>0.67</v>
       </c>
-      <c r="B134" s="27">
+      <c r="B134" s="60">
         <f>계산기!$C$7*계산기!$C$8/A134</f>
         <v/>
       </c>
-      <c r="C134" s="27">
+      <c r="C134" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A134/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D134" s="27">
+      <c r="D134" s="60">
         <f>IF(C134&lt;=계산기!$C$22/2,C134,계산기!$C$22*(1-계산기!$C$22/(4*C134)))</f>
         <v/>
       </c>
-      <c r="E134" s="27">
+      <c r="E134" s="60">
         <f>MIN(D134/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5070,22 +6533,22 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="26" t="n">
+      <c r="A135" s="59" t="n">
         <v>0.675</v>
       </c>
-      <c r="B135" s="27">
+      <c r="B135" s="60">
         <f>계산기!$C$7*계산기!$C$8/A135</f>
         <v/>
       </c>
-      <c r="C135" s="27">
+      <c r="C135" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A135/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D135" s="27">
+      <c r="D135" s="60">
         <f>IF(C135&lt;=계산기!$C$22/2,C135,계산기!$C$22*(1-계산기!$C$22/(4*C135)))</f>
         <v/>
       </c>
-      <c r="E135" s="27">
+      <c r="E135" s="60">
         <f>MIN(D135/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5095,22 +6558,22 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="26" t="n">
+      <c r="A136" s="59" t="n">
         <v>0.68</v>
       </c>
-      <c r="B136" s="27">
+      <c r="B136" s="60">
         <f>계산기!$C$7*계산기!$C$8/A136</f>
         <v/>
       </c>
-      <c r="C136" s="27">
+      <c r="C136" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A136/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D136" s="27">
+      <c r="D136" s="60">
         <f>IF(C136&lt;=계산기!$C$22/2,C136,계산기!$C$22*(1-계산기!$C$22/(4*C136)))</f>
         <v/>
       </c>
-      <c r="E136" s="27">
+      <c r="E136" s="60">
         <f>MIN(D136/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5120,22 +6583,22 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="26" t="n">
+      <c r="A137" s="59" t="n">
         <v>0.6850000000000001</v>
       </c>
-      <c r="B137" s="27">
+      <c r="B137" s="60">
         <f>계산기!$C$7*계산기!$C$8/A137</f>
         <v/>
       </c>
-      <c r="C137" s="27">
+      <c r="C137" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A137/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D137" s="27">
+      <c r="D137" s="60">
         <f>IF(C137&lt;=계산기!$C$22/2,C137,계산기!$C$22*(1-계산기!$C$22/(4*C137)))</f>
         <v/>
       </c>
-      <c r="E137" s="27">
+      <c r="E137" s="60">
         <f>MIN(D137/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5145,22 +6608,22 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="26" t="n">
+      <c r="A138" s="59" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="B138" s="27">
+      <c r="B138" s="60">
         <f>계산기!$C$7*계산기!$C$8/A138</f>
         <v/>
       </c>
-      <c r="C138" s="27">
+      <c r="C138" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A138/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D138" s="27">
+      <c r="D138" s="60">
         <f>IF(C138&lt;=계산기!$C$22/2,C138,계산기!$C$22*(1-계산기!$C$22/(4*C138)))</f>
         <v/>
       </c>
-      <c r="E138" s="27">
+      <c r="E138" s="60">
         <f>MIN(D138/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5170,22 +6633,22 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="26" t="n">
+      <c r="A139" s="59" t="n">
         <v>0.695</v>
       </c>
-      <c r="B139" s="27">
+      <c r="B139" s="60">
         <f>계산기!$C$7*계산기!$C$8/A139</f>
         <v/>
       </c>
-      <c r="C139" s="27">
+      <c r="C139" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A139/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D139" s="27">
+      <c r="D139" s="60">
         <f>IF(C139&lt;=계산기!$C$22/2,C139,계산기!$C$22*(1-계산기!$C$22/(4*C139)))</f>
         <v/>
       </c>
-      <c r="E139" s="27">
+      <c r="E139" s="60">
         <f>MIN(D139/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5195,22 +6658,22 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="26" t="n">
+      <c r="A140" s="59" t="n">
         <v>0.7</v>
       </c>
-      <c r="B140" s="27">
+      <c r="B140" s="60">
         <f>계산기!$C$7*계산기!$C$8/A140</f>
         <v/>
       </c>
-      <c r="C140" s="27">
+      <c r="C140" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A140/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D140" s="27">
+      <c r="D140" s="60">
         <f>IF(C140&lt;=계산기!$C$22/2,C140,계산기!$C$22*(1-계산기!$C$22/(4*C140)))</f>
         <v/>
       </c>
-      <c r="E140" s="27">
+      <c r="E140" s="60">
         <f>MIN(D140/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5220,22 +6683,22 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="26" t="n">
+      <c r="A141" s="59" t="n">
         <v>0.705</v>
       </c>
-      <c r="B141" s="27">
+      <c r="B141" s="60">
         <f>계산기!$C$7*계산기!$C$8/A141</f>
         <v/>
       </c>
-      <c r="C141" s="27">
+      <c r="C141" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A141/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D141" s="27">
+      <c r="D141" s="60">
         <f>IF(C141&lt;=계산기!$C$22/2,C141,계산기!$C$22*(1-계산기!$C$22/(4*C141)))</f>
         <v/>
       </c>
-      <c r="E141" s="27">
+      <c r="E141" s="60">
         <f>MIN(D141/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5245,22 +6708,22 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="26" t="n">
+      <c r="A142" s="59" t="n">
         <v>0.71</v>
       </c>
-      <c r="B142" s="27">
+      <c r="B142" s="60">
         <f>계산기!$C$7*계산기!$C$8/A142</f>
         <v/>
       </c>
-      <c r="C142" s="27">
+      <c r="C142" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A142/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D142" s="27">
+      <c r="D142" s="60">
         <f>IF(C142&lt;=계산기!$C$22/2,C142,계산기!$C$22*(1-계산기!$C$22/(4*C142)))</f>
         <v/>
       </c>
-      <c r="E142" s="27">
+      <c r="E142" s="60">
         <f>MIN(D142/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5270,22 +6733,22 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="26" t="n">
+      <c r="A143" s="59" t="n">
         <v>0.715</v>
       </c>
-      <c r="B143" s="27">
+      <c r="B143" s="60">
         <f>계산기!$C$7*계산기!$C$8/A143</f>
         <v/>
       </c>
-      <c r="C143" s="27">
+      <c r="C143" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A143/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D143" s="27">
+      <c r="D143" s="60">
         <f>IF(C143&lt;=계산기!$C$22/2,C143,계산기!$C$22*(1-계산기!$C$22/(4*C143)))</f>
         <v/>
       </c>
-      <c r="E143" s="27">
+      <c r="E143" s="60">
         <f>MIN(D143/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5295,22 +6758,22 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="26" t="n">
+      <c r="A144" s="59" t="n">
         <v>0.72</v>
       </c>
-      <c r="B144" s="27">
+      <c r="B144" s="60">
         <f>계산기!$C$7*계산기!$C$8/A144</f>
         <v/>
       </c>
-      <c r="C144" s="27">
+      <c r="C144" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A144/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D144" s="27">
+      <c r="D144" s="60">
         <f>IF(C144&lt;=계산기!$C$22/2,C144,계산기!$C$22*(1-계산기!$C$22/(4*C144)))</f>
         <v/>
       </c>
-      <c r="E144" s="27">
+      <c r="E144" s="60">
         <f>MIN(D144/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5320,22 +6783,22 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="26" t="n">
+      <c r="A145" s="59" t="n">
         <v>0.725</v>
       </c>
-      <c r="B145" s="27">
+      <c r="B145" s="60">
         <f>계산기!$C$7*계산기!$C$8/A145</f>
         <v/>
       </c>
-      <c r="C145" s="27">
+      <c r="C145" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A145/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D145" s="27">
+      <c r="D145" s="60">
         <f>IF(C145&lt;=계산기!$C$22/2,C145,계산기!$C$22*(1-계산기!$C$22/(4*C145)))</f>
         <v/>
       </c>
-      <c r="E145" s="27">
+      <c r="E145" s="60">
         <f>MIN(D145/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5345,22 +6808,22 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="26" t="n">
+      <c r="A146" s="59" t="n">
         <v>0.73</v>
       </c>
-      <c r="B146" s="27">
+      <c r="B146" s="60">
         <f>계산기!$C$7*계산기!$C$8/A146</f>
         <v/>
       </c>
-      <c r="C146" s="27">
+      <c r="C146" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A146/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D146" s="27">
+      <c r="D146" s="60">
         <f>IF(C146&lt;=계산기!$C$22/2,C146,계산기!$C$22*(1-계산기!$C$22/(4*C146)))</f>
         <v/>
       </c>
-      <c r="E146" s="27">
+      <c r="E146" s="60">
         <f>MIN(D146/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5370,22 +6833,22 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="26" t="n">
+      <c r="A147" s="59" t="n">
         <v>0.735</v>
       </c>
-      <c r="B147" s="27">
+      <c r="B147" s="60">
         <f>계산기!$C$7*계산기!$C$8/A147</f>
         <v/>
       </c>
-      <c r="C147" s="27">
+      <c r="C147" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A147/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D147" s="27">
+      <c r="D147" s="60">
         <f>IF(C147&lt;=계산기!$C$22/2,C147,계산기!$C$22*(1-계산기!$C$22/(4*C147)))</f>
         <v/>
       </c>
-      <c r="E147" s="27">
+      <c r="E147" s="60">
         <f>MIN(D147/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5395,22 +6858,22 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="26" t="n">
+      <c r="A148" s="59" t="n">
         <v>0.74</v>
       </c>
-      <c r="B148" s="27">
+      <c r="B148" s="60">
         <f>계산기!$C$7*계산기!$C$8/A148</f>
         <v/>
       </c>
-      <c r="C148" s="27">
+      <c r="C148" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A148/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D148" s="27">
+      <c r="D148" s="60">
         <f>IF(C148&lt;=계산기!$C$22/2,C148,계산기!$C$22*(1-계산기!$C$22/(4*C148)))</f>
         <v/>
       </c>
-      <c r="E148" s="27">
+      <c r="E148" s="60">
         <f>MIN(D148/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5420,22 +6883,22 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="26" t="n">
+      <c r="A149" s="59" t="n">
         <v>0.745</v>
       </c>
-      <c r="B149" s="27">
+      <c r="B149" s="60">
         <f>계산기!$C$7*계산기!$C$8/A149</f>
         <v/>
       </c>
-      <c r="C149" s="27">
+      <c r="C149" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A149/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D149" s="27">
+      <c r="D149" s="60">
         <f>IF(C149&lt;=계산기!$C$22/2,C149,계산기!$C$22*(1-계산기!$C$22/(4*C149)))</f>
         <v/>
       </c>
-      <c r="E149" s="27">
+      <c r="E149" s="60">
         <f>MIN(D149/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5445,22 +6908,22 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="26" t="n">
+      <c r="A150" s="59" t="n">
         <v>0.75</v>
       </c>
-      <c r="B150" s="27">
+      <c r="B150" s="60">
         <f>계산기!$C$7*계산기!$C$8/A150</f>
         <v/>
       </c>
-      <c r="C150" s="27">
+      <c r="C150" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A150/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D150" s="27">
+      <c r="D150" s="60">
         <f>IF(C150&lt;=계산기!$C$22/2,C150,계산기!$C$22*(1-계산기!$C$22/(4*C150)))</f>
         <v/>
       </c>
-      <c r="E150" s="27">
+      <c r="E150" s="60">
         <f>MIN(D150/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5470,22 +6933,22 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="26" t="n">
+      <c r="A151" s="59" t="n">
         <v>0.755</v>
       </c>
-      <c r="B151" s="27">
+      <c r="B151" s="60">
         <f>계산기!$C$7*계산기!$C$8/A151</f>
         <v/>
       </c>
-      <c r="C151" s="27">
+      <c r="C151" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A151/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D151" s="27">
+      <c r="D151" s="60">
         <f>IF(C151&lt;=계산기!$C$22/2,C151,계산기!$C$22*(1-계산기!$C$22/(4*C151)))</f>
         <v/>
       </c>
-      <c r="E151" s="27">
+      <c r="E151" s="60">
         <f>MIN(D151/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5495,22 +6958,22 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="26" t="n">
+      <c r="A152" s="59" t="n">
         <v>0.76</v>
       </c>
-      <c r="B152" s="27">
+      <c r="B152" s="60">
         <f>계산기!$C$7*계산기!$C$8/A152</f>
         <v/>
       </c>
-      <c r="C152" s="27">
+      <c r="C152" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A152/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D152" s="27">
+      <c r="D152" s="60">
         <f>IF(C152&lt;=계산기!$C$22/2,C152,계산기!$C$22*(1-계산기!$C$22/(4*C152)))</f>
         <v/>
       </c>
-      <c r="E152" s="27">
+      <c r="E152" s="60">
         <f>MIN(D152/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5520,22 +6983,22 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="26" t="n">
+      <c r="A153" s="59" t="n">
         <v>0.765</v>
       </c>
-      <c r="B153" s="27">
+      <c r="B153" s="60">
         <f>계산기!$C$7*계산기!$C$8/A153</f>
         <v/>
       </c>
-      <c r="C153" s="27">
+      <c r="C153" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A153/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D153" s="27">
+      <c r="D153" s="60">
         <f>IF(C153&lt;=계산기!$C$22/2,C153,계산기!$C$22*(1-계산기!$C$22/(4*C153)))</f>
         <v/>
       </c>
-      <c r="E153" s="27">
+      <c r="E153" s="60">
         <f>MIN(D153/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5545,22 +7008,22 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="26" t="n">
+      <c r="A154" s="59" t="n">
         <v>0.77</v>
       </c>
-      <c r="B154" s="27">
+      <c r="B154" s="60">
         <f>계산기!$C$7*계산기!$C$8/A154</f>
         <v/>
       </c>
-      <c r="C154" s="27">
+      <c r="C154" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A154/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D154" s="27">
+      <c r="D154" s="60">
         <f>IF(C154&lt;=계산기!$C$22/2,C154,계산기!$C$22*(1-계산기!$C$22/(4*C154)))</f>
         <v/>
       </c>
-      <c r="E154" s="27">
+      <c r="E154" s="60">
         <f>MIN(D154/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5570,22 +7033,22 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="26" t="n">
+      <c r="A155" s="59" t="n">
         <v>0.775</v>
       </c>
-      <c r="B155" s="27">
+      <c r="B155" s="60">
         <f>계산기!$C$7*계산기!$C$8/A155</f>
         <v/>
       </c>
-      <c r="C155" s="27">
+      <c r="C155" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A155/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D155" s="27">
+      <c r="D155" s="60">
         <f>IF(C155&lt;=계산기!$C$22/2,C155,계산기!$C$22*(1-계산기!$C$22/(4*C155)))</f>
         <v/>
       </c>
-      <c r="E155" s="27">
+      <c r="E155" s="60">
         <f>MIN(D155/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5595,22 +7058,22 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="26" t="n">
+      <c r="A156" s="59" t="n">
         <v>0.78</v>
       </c>
-      <c r="B156" s="27">
+      <c r="B156" s="60">
         <f>계산기!$C$7*계산기!$C$8/A156</f>
         <v/>
       </c>
-      <c r="C156" s="27">
+      <c r="C156" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A156/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D156" s="27">
+      <c r="D156" s="60">
         <f>IF(C156&lt;=계산기!$C$22/2,C156,계산기!$C$22*(1-계산기!$C$22/(4*C156)))</f>
         <v/>
       </c>
-      <c r="E156" s="27">
+      <c r="E156" s="60">
         <f>MIN(D156/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5620,22 +7083,22 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="26" t="n">
+      <c r="A157" s="59" t="n">
         <v>0.785</v>
       </c>
-      <c r="B157" s="27">
+      <c r="B157" s="60">
         <f>계산기!$C$7*계산기!$C$8/A157</f>
         <v/>
       </c>
-      <c r="C157" s="27">
+      <c r="C157" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A157/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D157" s="27">
+      <c r="D157" s="60">
         <f>IF(C157&lt;=계산기!$C$22/2,C157,계산기!$C$22*(1-계산기!$C$22/(4*C157)))</f>
         <v/>
       </c>
-      <c r="E157" s="27">
+      <c r="E157" s="60">
         <f>MIN(D157/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5645,22 +7108,22 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="26" t="n">
+      <c r="A158" s="59" t="n">
         <v>0.79</v>
       </c>
-      <c r="B158" s="27">
+      <c r="B158" s="60">
         <f>계산기!$C$7*계산기!$C$8/A158</f>
         <v/>
       </c>
-      <c r="C158" s="27">
+      <c r="C158" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A158/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D158" s="27">
+      <c r="D158" s="60">
         <f>IF(C158&lt;=계산기!$C$22/2,C158,계산기!$C$22*(1-계산기!$C$22/(4*C158)))</f>
         <v/>
       </c>
-      <c r="E158" s="27">
+      <c r="E158" s="60">
         <f>MIN(D158/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5670,22 +7133,22 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="26" t="n">
+      <c r="A159" s="59" t="n">
         <v>0.795</v>
       </c>
-      <c r="B159" s="27">
+      <c r="B159" s="60">
         <f>계산기!$C$7*계산기!$C$8/A159</f>
         <v/>
       </c>
-      <c r="C159" s="27">
+      <c r="C159" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A159/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D159" s="27">
+      <c r="D159" s="60">
         <f>IF(C159&lt;=계산기!$C$22/2,C159,계산기!$C$22*(1-계산기!$C$22/(4*C159)))</f>
         <v/>
       </c>
-      <c r="E159" s="27">
+      <c r="E159" s="60">
         <f>MIN(D159/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5695,22 +7158,22 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="26" t="n">
+      <c r="A160" s="59" t="n">
         <v>0.8</v>
       </c>
-      <c r="B160" s="27">
+      <c r="B160" s="60">
         <f>계산기!$C$7*계산기!$C$8/A160</f>
         <v/>
       </c>
-      <c r="C160" s="27">
+      <c r="C160" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A160/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D160" s="27">
+      <c r="D160" s="60">
         <f>IF(C160&lt;=계산기!$C$22/2,C160,계산기!$C$22*(1-계산기!$C$22/(4*C160)))</f>
         <v/>
       </c>
-      <c r="E160" s="27">
+      <c r="E160" s="60">
         <f>MIN(D160/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5720,22 +7183,22 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="26" t="n">
+      <c r="A161" s="59" t="n">
         <v>0.805</v>
       </c>
-      <c r="B161" s="27">
+      <c r="B161" s="60">
         <f>계산기!$C$7*계산기!$C$8/A161</f>
         <v/>
       </c>
-      <c r="C161" s="27">
+      <c r="C161" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A161/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D161" s="27">
+      <c r="D161" s="60">
         <f>IF(C161&lt;=계산기!$C$22/2,C161,계산기!$C$22*(1-계산기!$C$22/(4*C161)))</f>
         <v/>
       </c>
-      <c r="E161" s="27">
+      <c r="E161" s="60">
         <f>MIN(D161/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5745,22 +7208,22 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="26" t="n">
+      <c r="A162" s="59" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="B162" s="27">
+      <c r="B162" s="60">
         <f>계산기!$C$7*계산기!$C$8/A162</f>
         <v/>
       </c>
-      <c r="C162" s="27">
+      <c r="C162" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A162/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D162" s="27">
+      <c r="D162" s="60">
         <f>IF(C162&lt;=계산기!$C$22/2,C162,계산기!$C$22*(1-계산기!$C$22/(4*C162)))</f>
         <v/>
       </c>
-      <c r="E162" s="27">
+      <c r="E162" s="60">
         <f>MIN(D162/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5770,22 +7233,22 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="26" t="n">
+      <c r="A163" s="59" t="n">
         <v>0.8149999999999999</v>
       </c>
-      <c r="B163" s="27">
+      <c r="B163" s="60">
         <f>계산기!$C$7*계산기!$C$8/A163</f>
         <v/>
       </c>
-      <c r="C163" s="27">
+      <c r="C163" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A163/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D163" s="27">
+      <c r="D163" s="60">
         <f>IF(C163&lt;=계산기!$C$22/2,C163,계산기!$C$22*(1-계산기!$C$22/(4*C163)))</f>
         <v/>
       </c>
-      <c r="E163" s="27">
+      <c r="E163" s="60">
         <f>MIN(D163/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5795,22 +7258,22 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="26" t="n">
+      <c r="A164" s="59" t="n">
         <v>0.82</v>
       </c>
-      <c r="B164" s="27">
+      <c r="B164" s="60">
         <f>계산기!$C$7*계산기!$C$8/A164</f>
         <v/>
       </c>
-      <c r="C164" s="27">
+      <c r="C164" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A164/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D164" s="27">
+      <c r="D164" s="60">
         <f>IF(C164&lt;=계산기!$C$22/2,C164,계산기!$C$22*(1-계산기!$C$22/(4*C164)))</f>
         <v/>
       </c>
-      <c r="E164" s="27">
+      <c r="E164" s="60">
         <f>MIN(D164/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5820,22 +7283,22 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="26" t="n">
+      <c r="A165" s="59" t="n">
         <v>0.825</v>
       </c>
-      <c r="B165" s="27">
+      <c r="B165" s="60">
         <f>계산기!$C$7*계산기!$C$8/A165</f>
         <v/>
       </c>
-      <c r="C165" s="27">
+      <c r="C165" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A165/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D165" s="27">
+      <c r="D165" s="60">
         <f>IF(C165&lt;=계산기!$C$22/2,C165,계산기!$C$22*(1-계산기!$C$22/(4*C165)))</f>
         <v/>
       </c>
-      <c r="E165" s="27">
+      <c r="E165" s="60">
         <f>MIN(D165/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5845,22 +7308,22 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="26" t="n">
+      <c r="A166" s="59" t="n">
         <v>0.83</v>
       </c>
-      <c r="B166" s="27">
+      <c r="B166" s="60">
         <f>계산기!$C$7*계산기!$C$8/A166</f>
         <v/>
       </c>
-      <c r="C166" s="27">
+      <c r="C166" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A166/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D166" s="27">
+      <c r="D166" s="60">
         <f>IF(C166&lt;=계산기!$C$22/2,C166,계산기!$C$22*(1-계산기!$C$22/(4*C166)))</f>
         <v/>
       </c>
-      <c r="E166" s="27">
+      <c r="E166" s="60">
         <f>MIN(D166/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5870,22 +7333,22 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="26" t="n">
+      <c r="A167" s="59" t="n">
         <v>0.835</v>
       </c>
-      <c r="B167" s="27">
+      <c r="B167" s="60">
         <f>계산기!$C$7*계산기!$C$8/A167</f>
         <v/>
       </c>
-      <c r="C167" s="27">
+      <c r="C167" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A167/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D167" s="27">
+      <c r="D167" s="60">
         <f>IF(C167&lt;=계산기!$C$22/2,C167,계산기!$C$22*(1-계산기!$C$22/(4*C167)))</f>
         <v/>
       </c>
-      <c r="E167" s="27">
+      <c r="E167" s="60">
         <f>MIN(D167/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5895,22 +7358,22 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="26" t="n">
+      <c r="A168" s="59" t="n">
         <v>0.84</v>
       </c>
-      <c r="B168" s="27">
+      <c r="B168" s="60">
         <f>계산기!$C$7*계산기!$C$8/A168</f>
         <v/>
       </c>
-      <c r="C168" s="27">
+      <c r="C168" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A168/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D168" s="27">
+      <c r="D168" s="60">
         <f>IF(C168&lt;=계산기!$C$22/2,C168,계산기!$C$22*(1-계산기!$C$22/(4*C168)))</f>
         <v/>
       </c>
-      <c r="E168" s="27">
+      <c r="E168" s="60">
         <f>MIN(D168/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5920,22 +7383,22 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="26" t="n">
+      <c r="A169" s="59" t="n">
         <v>0.845</v>
       </c>
-      <c r="B169" s="27">
+      <c r="B169" s="60">
         <f>계산기!$C$7*계산기!$C$8/A169</f>
         <v/>
       </c>
-      <c r="C169" s="27">
+      <c r="C169" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A169/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D169" s="27">
+      <c r="D169" s="60">
         <f>IF(C169&lt;=계산기!$C$22/2,C169,계산기!$C$22*(1-계산기!$C$22/(4*C169)))</f>
         <v/>
       </c>
-      <c r="E169" s="27">
+      <c r="E169" s="60">
         <f>MIN(D169/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5945,22 +7408,22 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="26" t="n">
+      <c r="A170" s="59" t="n">
         <v>0.85</v>
       </c>
-      <c r="B170" s="27">
+      <c r="B170" s="60">
         <f>계산기!$C$7*계산기!$C$8/A170</f>
         <v/>
       </c>
-      <c r="C170" s="27">
+      <c r="C170" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A170/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D170" s="27">
+      <c r="D170" s="60">
         <f>IF(C170&lt;=계산기!$C$22/2,C170,계산기!$C$22*(1-계산기!$C$22/(4*C170)))</f>
         <v/>
       </c>
-      <c r="E170" s="27">
+      <c r="E170" s="60">
         <f>MIN(D170/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5970,22 +7433,22 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="26" t="n">
+      <c r="A171" s="59" t="n">
         <v>0.855</v>
       </c>
-      <c r="B171" s="27">
+      <c r="B171" s="60">
         <f>계산기!$C$7*계산기!$C$8/A171</f>
         <v/>
       </c>
-      <c r="C171" s="27">
+      <c r="C171" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A171/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D171" s="27">
+      <c r="D171" s="60">
         <f>IF(C171&lt;=계산기!$C$22/2,C171,계산기!$C$22*(1-계산기!$C$22/(4*C171)))</f>
         <v/>
       </c>
-      <c r="E171" s="27">
+      <c r="E171" s="60">
         <f>MIN(D171/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -5995,22 +7458,22 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="26" t="n">
+      <c r="A172" s="59" t="n">
         <v>0.86</v>
       </c>
-      <c r="B172" s="27">
+      <c r="B172" s="60">
         <f>계산기!$C$7*계산기!$C$8/A172</f>
         <v/>
       </c>
-      <c r="C172" s="27">
+      <c r="C172" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A172/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D172" s="27">
+      <c r="D172" s="60">
         <f>IF(C172&lt;=계산기!$C$22/2,C172,계산기!$C$22*(1-계산기!$C$22/(4*C172)))</f>
         <v/>
       </c>
-      <c r="E172" s="27">
+      <c r="E172" s="60">
         <f>MIN(D172/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6020,22 +7483,22 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="26" t="n">
+      <c r="A173" s="59" t="n">
         <v>0.865</v>
       </c>
-      <c r="B173" s="27">
+      <c r="B173" s="60">
         <f>계산기!$C$7*계산기!$C$8/A173</f>
         <v/>
       </c>
-      <c r="C173" s="27">
+      <c r="C173" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A173/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D173" s="27">
+      <c r="D173" s="60">
         <f>IF(C173&lt;=계산기!$C$22/2,C173,계산기!$C$22*(1-계산기!$C$22/(4*C173)))</f>
         <v/>
       </c>
-      <c r="E173" s="27">
+      <c r="E173" s="60">
         <f>MIN(D173/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6045,22 +7508,22 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="26" t="n">
+      <c r="A174" s="59" t="n">
         <v>0.87</v>
       </c>
-      <c r="B174" s="27">
+      <c r="B174" s="60">
         <f>계산기!$C$7*계산기!$C$8/A174</f>
         <v/>
       </c>
-      <c r="C174" s="27">
+      <c r="C174" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A174/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D174" s="27">
+      <c r="D174" s="60">
         <f>IF(C174&lt;=계산기!$C$22/2,C174,계산기!$C$22*(1-계산기!$C$22/(4*C174)))</f>
         <v/>
       </c>
-      <c r="E174" s="27">
+      <c r="E174" s="60">
         <f>MIN(D174/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6070,22 +7533,22 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="26" t="n">
+      <c r="A175" s="59" t="n">
         <v>0.875</v>
       </c>
-      <c r="B175" s="27">
+      <c r="B175" s="60">
         <f>계산기!$C$7*계산기!$C$8/A175</f>
         <v/>
       </c>
-      <c r="C175" s="27">
+      <c r="C175" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A175/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D175" s="27">
+      <c r="D175" s="60">
         <f>IF(C175&lt;=계산기!$C$22/2,C175,계산기!$C$22*(1-계산기!$C$22/(4*C175)))</f>
         <v/>
       </c>
-      <c r="E175" s="27">
+      <c r="E175" s="60">
         <f>MIN(D175/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6095,22 +7558,22 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="26" t="n">
+      <c r="A176" s="59" t="n">
         <v>0.88</v>
       </c>
-      <c r="B176" s="27">
+      <c r="B176" s="60">
         <f>계산기!$C$7*계산기!$C$8/A176</f>
         <v/>
       </c>
-      <c r="C176" s="27">
+      <c r="C176" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A176/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D176" s="27">
+      <c r="D176" s="60">
         <f>IF(C176&lt;=계산기!$C$22/2,C176,계산기!$C$22*(1-계산기!$C$22/(4*C176)))</f>
         <v/>
       </c>
-      <c r="E176" s="27">
+      <c r="E176" s="60">
         <f>MIN(D176/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6120,22 +7583,22 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="26" t="n">
+      <c r="A177" s="59" t="n">
         <v>0.885</v>
       </c>
-      <c r="B177" s="27">
+      <c r="B177" s="60">
         <f>계산기!$C$7*계산기!$C$8/A177</f>
         <v/>
       </c>
-      <c r="C177" s="27">
+      <c r="C177" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A177/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D177" s="27">
+      <c r="D177" s="60">
         <f>IF(C177&lt;=계산기!$C$22/2,C177,계산기!$C$22*(1-계산기!$C$22/(4*C177)))</f>
         <v/>
       </c>
-      <c r="E177" s="27">
+      <c r="E177" s="60">
         <f>MIN(D177/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6145,22 +7608,22 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="26" t="n">
+      <c r="A178" s="59" t="n">
         <v>0.89</v>
       </c>
-      <c r="B178" s="27">
+      <c r="B178" s="60">
         <f>계산기!$C$7*계산기!$C$8/A178</f>
         <v/>
       </c>
-      <c r="C178" s="27">
+      <c r="C178" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A178/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D178" s="27">
+      <c r="D178" s="60">
         <f>IF(C178&lt;=계산기!$C$22/2,C178,계산기!$C$22*(1-계산기!$C$22/(4*C178)))</f>
         <v/>
       </c>
-      <c r="E178" s="27">
+      <c r="E178" s="60">
         <f>MIN(D178/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6170,22 +7633,22 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="26" t="n">
+      <c r="A179" s="59" t="n">
         <v>0.895</v>
       </c>
-      <c r="B179" s="27">
+      <c r="B179" s="60">
         <f>계산기!$C$7*계산기!$C$8/A179</f>
         <v/>
       </c>
-      <c r="C179" s="27">
+      <c r="C179" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A179/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D179" s="27">
+      <c r="D179" s="60">
         <f>IF(C179&lt;=계산기!$C$22/2,C179,계산기!$C$22*(1-계산기!$C$22/(4*C179)))</f>
         <v/>
       </c>
-      <c r="E179" s="27">
+      <c r="E179" s="60">
         <f>MIN(D179/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6195,22 +7658,22 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="26" t="n">
+      <c r="A180" s="59" t="n">
         <v>0.9</v>
       </c>
-      <c r="B180" s="27">
+      <c r="B180" s="60">
         <f>계산기!$C$7*계산기!$C$8/A180</f>
         <v/>
       </c>
-      <c r="C180" s="27">
+      <c r="C180" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A180/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D180" s="27">
+      <c r="D180" s="60">
         <f>IF(C180&lt;=계산기!$C$22/2,C180,계산기!$C$22*(1-계산기!$C$22/(4*C180)))</f>
         <v/>
       </c>
-      <c r="E180" s="27">
+      <c r="E180" s="60">
         <f>MIN(D180/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6220,22 +7683,22 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="26" t="n">
+      <c r="A181" s="59" t="n">
         <v>0.905</v>
       </c>
-      <c r="B181" s="27">
+      <c r="B181" s="60">
         <f>계산기!$C$7*계산기!$C$8/A181</f>
         <v/>
       </c>
-      <c r="C181" s="27">
+      <c r="C181" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A181/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D181" s="27">
+      <c r="D181" s="60">
         <f>IF(C181&lt;=계산기!$C$22/2,C181,계산기!$C$22*(1-계산기!$C$22/(4*C181)))</f>
         <v/>
       </c>
-      <c r="E181" s="27">
+      <c r="E181" s="60">
         <f>MIN(D181/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6245,22 +7708,22 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="26" t="n">
+      <c r="A182" s="59" t="n">
         <v>0.91</v>
       </c>
-      <c r="B182" s="27">
+      <c r="B182" s="60">
         <f>계산기!$C$7*계산기!$C$8/A182</f>
         <v/>
       </c>
-      <c r="C182" s="27">
+      <c r="C182" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A182/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D182" s="27">
+      <c r="D182" s="60">
         <f>IF(C182&lt;=계산기!$C$22/2,C182,계산기!$C$22*(1-계산기!$C$22/(4*C182)))</f>
         <v/>
       </c>
-      <c r="E182" s="27">
+      <c r="E182" s="60">
         <f>MIN(D182/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6270,22 +7733,22 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="26" t="n">
+      <c r="A183" s="59" t="n">
         <v>0.915</v>
       </c>
-      <c r="B183" s="27">
+      <c r="B183" s="60">
         <f>계산기!$C$7*계산기!$C$8/A183</f>
         <v/>
       </c>
-      <c r="C183" s="27">
+      <c r="C183" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A183/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D183" s="27">
+      <c r="D183" s="60">
         <f>IF(C183&lt;=계산기!$C$22/2,C183,계산기!$C$22*(1-계산기!$C$22/(4*C183)))</f>
         <v/>
       </c>
-      <c r="E183" s="27">
+      <c r="E183" s="60">
         <f>MIN(D183/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6295,22 +7758,22 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="26" t="n">
+      <c r="A184" s="59" t="n">
         <v>0.92</v>
       </c>
-      <c r="B184" s="27">
+      <c r="B184" s="60">
         <f>계산기!$C$7*계산기!$C$8/A184</f>
         <v/>
       </c>
-      <c r="C184" s="27">
+      <c r="C184" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A184/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D184" s="27">
+      <c r="D184" s="60">
         <f>IF(C184&lt;=계산기!$C$22/2,C184,계산기!$C$22*(1-계산기!$C$22/(4*C184)))</f>
         <v/>
       </c>
-      <c r="E184" s="27">
+      <c r="E184" s="60">
         <f>MIN(D184/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6320,22 +7783,22 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="26" t="n">
+      <c r="A185" s="59" t="n">
         <v>0.925</v>
       </c>
-      <c r="B185" s="27">
+      <c r="B185" s="60">
         <f>계산기!$C$7*계산기!$C$8/A185</f>
         <v/>
       </c>
-      <c r="C185" s="27">
+      <c r="C185" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A185/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D185" s="27">
+      <c r="D185" s="60">
         <f>IF(C185&lt;=계산기!$C$22/2,C185,계산기!$C$22*(1-계산기!$C$22/(4*C185)))</f>
         <v/>
       </c>
-      <c r="E185" s="27">
+      <c r="E185" s="60">
         <f>MIN(D185/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6345,22 +7808,22 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="26" t="n">
+      <c r="A186" s="59" t="n">
         <v>0.93</v>
       </c>
-      <c r="B186" s="27">
+      <c r="B186" s="60">
         <f>계산기!$C$7*계산기!$C$8/A186</f>
         <v/>
       </c>
-      <c r="C186" s="27">
+      <c r="C186" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A186/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D186" s="27">
+      <c r="D186" s="60">
         <f>IF(C186&lt;=계산기!$C$22/2,C186,계산기!$C$22*(1-계산기!$C$22/(4*C186)))</f>
         <v/>
       </c>
-      <c r="E186" s="27">
+      <c r="E186" s="60">
         <f>MIN(D186/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6370,22 +7833,22 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="26" t="n">
+      <c r="A187" s="59" t="n">
         <v>0.9350000000000001</v>
       </c>
-      <c r="B187" s="27">
+      <c r="B187" s="60">
         <f>계산기!$C$7*계산기!$C$8/A187</f>
         <v/>
       </c>
-      <c r="C187" s="27">
+      <c r="C187" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A187/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D187" s="27">
+      <c r="D187" s="60">
         <f>IF(C187&lt;=계산기!$C$22/2,C187,계산기!$C$22*(1-계산기!$C$22/(4*C187)))</f>
         <v/>
       </c>
-      <c r="E187" s="27">
+      <c r="E187" s="60">
         <f>MIN(D187/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6395,22 +7858,22 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="26" t="n">
+      <c r="A188" s="59" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="B188" s="27">
+      <c r="B188" s="60">
         <f>계산기!$C$7*계산기!$C$8/A188</f>
         <v/>
       </c>
-      <c r="C188" s="27">
+      <c r="C188" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A188/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D188" s="27">
+      <c r="D188" s="60">
         <f>IF(C188&lt;=계산기!$C$22/2,C188,계산기!$C$22*(1-계산기!$C$22/(4*C188)))</f>
         <v/>
       </c>
-      <c r="E188" s="27">
+      <c r="E188" s="60">
         <f>MIN(D188/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6420,22 +7883,22 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="26" t="n">
+      <c r="A189" s="59" t="n">
         <v>0.945</v>
       </c>
-      <c r="B189" s="27">
+      <c r="B189" s="60">
         <f>계산기!$C$7*계산기!$C$8/A189</f>
         <v/>
       </c>
-      <c r="C189" s="27">
+      <c r="C189" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A189/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D189" s="27">
+      <c r="D189" s="60">
         <f>IF(C189&lt;=계산기!$C$22/2,C189,계산기!$C$22*(1-계산기!$C$22/(4*C189)))</f>
         <v/>
       </c>
-      <c r="E189" s="27">
+      <c r="E189" s="60">
         <f>MIN(D189/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6445,22 +7908,22 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="26" t="n">
+      <c r="A190" s="59" t="n">
         <v>0.95</v>
       </c>
-      <c r="B190" s="27">
+      <c r="B190" s="60">
         <f>계산기!$C$7*계산기!$C$8/A190</f>
         <v/>
       </c>
-      <c r="C190" s="27">
+      <c r="C190" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A190/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D190" s="27">
+      <c r="D190" s="60">
         <f>IF(C190&lt;=계산기!$C$22/2,C190,계산기!$C$22*(1-계산기!$C$22/(4*C190)))</f>
         <v/>
       </c>
-      <c r="E190" s="27">
+      <c r="E190" s="60">
         <f>MIN(D190/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6470,22 +7933,22 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="26" t="n">
+      <c r="A191" s="59" t="n">
         <v>0.955</v>
       </c>
-      <c r="B191" s="27">
+      <c r="B191" s="60">
         <f>계산기!$C$7*계산기!$C$8/A191</f>
         <v/>
       </c>
-      <c r="C191" s="27">
+      <c r="C191" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A191/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D191" s="27">
+      <c r="D191" s="60">
         <f>IF(C191&lt;=계산기!$C$22/2,C191,계산기!$C$22*(1-계산기!$C$22/(4*C191)))</f>
         <v/>
       </c>
-      <c r="E191" s="27">
+      <c r="E191" s="60">
         <f>MIN(D191/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6495,22 +7958,22 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="26" t="n">
+      <c r="A192" s="59" t="n">
         <v>0.96</v>
       </c>
-      <c r="B192" s="27">
+      <c r="B192" s="60">
         <f>계산기!$C$7*계산기!$C$8/A192</f>
         <v/>
       </c>
-      <c r="C192" s="27">
+      <c r="C192" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A192/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D192" s="27">
+      <c r="D192" s="60">
         <f>IF(C192&lt;=계산기!$C$22/2,C192,계산기!$C$22*(1-계산기!$C$22/(4*C192)))</f>
         <v/>
       </c>
-      <c r="E192" s="27">
+      <c r="E192" s="60">
         <f>MIN(D192/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6520,22 +7983,22 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="26" t="n">
+      <c r="A193" s="59" t="n">
         <v>0.965</v>
       </c>
-      <c r="B193" s="27">
+      <c r="B193" s="60">
         <f>계산기!$C$7*계산기!$C$8/A193</f>
         <v/>
       </c>
-      <c r="C193" s="27">
+      <c r="C193" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A193/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D193" s="27">
+      <c r="D193" s="60">
         <f>IF(C193&lt;=계산기!$C$22/2,C193,계산기!$C$22*(1-계산기!$C$22/(4*C193)))</f>
         <v/>
       </c>
-      <c r="E193" s="27">
+      <c r="E193" s="60">
         <f>MIN(D193/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6545,22 +8008,22 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="26" t="n">
+      <c r="A194" s="59" t="n">
         <v>0.97</v>
       </c>
-      <c r="B194" s="27">
+      <c r="B194" s="60">
         <f>계산기!$C$7*계산기!$C$8/A194</f>
         <v/>
       </c>
-      <c r="C194" s="27">
+      <c r="C194" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A194/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D194" s="27">
+      <c r="D194" s="60">
         <f>IF(C194&lt;=계산기!$C$22/2,C194,계산기!$C$22*(1-계산기!$C$22/(4*C194)))</f>
         <v/>
       </c>
-      <c r="E194" s="27">
+      <c r="E194" s="60">
         <f>MIN(D194/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6570,22 +8033,22 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="26" t="n">
+      <c r="A195" s="59" t="n">
         <v>0.975</v>
       </c>
-      <c r="B195" s="27">
+      <c r="B195" s="60">
         <f>계산기!$C$7*계산기!$C$8/A195</f>
         <v/>
       </c>
-      <c r="C195" s="27">
+      <c r="C195" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A195/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D195" s="27">
+      <c r="D195" s="60">
         <f>IF(C195&lt;=계산기!$C$22/2,C195,계산기!$C$22*(1-계산기!$C$22/(4*C195)))</f>
         <v/>
       </c>
-      <c r="E195" s="27">
+      <c r="E195" s="60">
         <f>MIN(D195/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6595,22 +8058,22 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="26" t="n">
+      <c r="A196" s="59" t="n">
         <v>0.98</v>
       </c>
-      <c r="B196" s="27">
+      <c r="B196" s="60">
         <f>계산기!$C$7*계산기!$C$8/A196</f>
         <v/>
       </c>
-      <c r="C196" s="27">
+      <c r="C196" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A196/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D196" s="27">
+      <c r="D196" s="60">
         <f>IF(C196&lt;=계산기!$C$22/2,C196,계산기!$C$22*(1-계산기!$C$22/(4*C196)))</f>
         <v/>
       </c>
-      <c r="E196" s="27">
+      <c r="E196" s="60">
         <f>MIN(D196/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6620,22 +8083,22 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="26" t="n">
+      <c r="A197" s="59" t="n">
         <v>0.985</v>
       </c>
-      <c r="B197" s="27">
+      <c r="B197" s="60">
         <f>계산기!$C$7*계산기!$C$8/A197</f>
         <v/>
       </c>
-      <c r="C197" s="27">
+      <c r="C197" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A197/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D197" s="27">
+      <c r="D197" s="60">
         <f>IF(C197&lt;=계산기!$C$22/2,C197,계산기!$C$22*(1-계산기!$C$22/(4*C197)))</f>
         <v/>
       </c>
-      <c r="E197" s="27">
+      <c r="E197" s="60">
         <f>MIN(D197/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6645,22 +8108,22 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="26" t="n">
+      <c r="A198" s="59" t="n">
         <v>0.99</v>
       </c>
-      <c r="B198" s="27">
+      <c r="B198" s="60">
         <f>계산기!$C$7*계산기!$C$8/A198</f>
         <v/>
       </c>
-      <c r="C198" s="27">
+      <c r="C198" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A198/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D198" s="27">
+      <c r="D198" s="60">
         <f>IF(C198&lt;=계산기!$C$22/2,C198,계산기!$C$22*(1-계산기!$C$22/(4*C198)))</f>
         <v/>
       </c>
-      <c r="E198" s="27">
+      <c r="E198" s="60">
         <f>MIN(D198/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6670,22 +8133,22 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="26" t="n">
+      <c r="A199" s="59" t="n">
         <v>0.995</v>
       </c>
-      <c r="B199" s="27">
+      <c r="B199" s="60">
         <f>계산기!$C$7*계산기!$C$8/A199</f>
         <v/>
       </c>
-      <c r="C199" s="27">
+      <c r="C199" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A199/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D199" s="27">
+      <c r="D199" s="60">
         <f>IF(C199&lt;=계산기!$C$22/2,C199,계산기!$C$22*(1-계산기!$C$22/(4*C199)))</f>
         <v/>
       </c>
-      <c r="E199" s="27">
+      <c r="E199" s="60">
         <f>MIN(D199/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6695,22 +8158,22 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="26" t="n">
+      <c r="A200" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="B200" s="27">
+      <c r="B200" s="60">
         <f>계산기!$C$7*계산기!$C$8/A200</f>
         <v/>
       </c>
-      <c r="C200" s="27">
+      <c r="C200" s="60">
         <f>PI()^2*계산기!$C$23/(12*(1-계산기!$C$18^2))*(A200/(계산기!$C$11*계산기!$C$10))^2</f>
         <v/>
       </c>
-      <c r="D200" s="27">
+      <c r="D200" s="60">
         <f>IF(C200&lt;=계산기!$C$22/2,C200,계산기!$C$22*(1-계산기!$C$22/(4*C200)))</f>
         <v/>
       </c>
-      <c r="E200" s="27">
+      <c r="E200" s="60">
         <f>MIN(D200/계산기!$C$19,계산기!$C$21)</f>
         <v/>
       </c>
@@ -6724,186 +8187,207 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="61" t="inlineStr">
         <is>
           <t>PFHE Plain 핀 적정두께 계산기 — 사용 안내</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="29" t="inlineStr"/>
+      <c r="A2" s="62" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="63" t="inlineStr">
         <is>
           <t>■ 사용법</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="62" t="inlineStr">
         <is>
           <t>1. [계산기] 시트의 파랑(노랑배경) 셀만 편집합니다. 나머지는 자동 계산 수식입니다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="62" t="inlineStr">
         <is>
           <t>2. 단위는 압력 MPa, 길이 mm 입니다 (1 MPa = 10 bar ≈ 10.2 kgf/cm²).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="62" t="inlineStr">
         <is>
           <t>3. [1][2]는 최소 소요두께, [3]은 채택 기준(둘 중 큰 값)입니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="62" t="inlineStr">
         <is>
           <t>4. t_sel(선정 두께)을 입력하면 ⑤ 검증에서 합/부를 판정합니다. 0이면 검증을 건너뜁니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="62" t="inlineStr">
         <is>
           <t>5. ΔP_c(압축)가 0이면 좌굴 검토는 생략됩니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr"/>
+      <c r="A9" s="62" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="63" t="inlineStr">
         <is>
           <t>■ 계산 근거 (수식)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="62" t="inlineStr">
         <is>
           <t>[1] 핀 인장:    t ≥ f·ΔP_t·p / (S(T) + f·ΔP_t)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="62" t="inlineStr">
         <is>
           <t>[2] 핀 좌굴:    ΔP_c·p/t ≤ min(σ_cr/DF, S), σ_cr는 오일러식 + Johnson 비탄성 천이</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">               → [좌굴스캔] 시트가 후보 두께를 훑어 조건을 만족하는 최소 t를 MINIFS로 반환</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="62" t="inlineStr">
         <is>
           <t>[3] 파팅시트:  t_ps ≥ √(4·M_d/S),  M_d = w·s²/12 + P_min·(p̄−t)·p̄/8</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="62" t="inlineStr">
         <is>
           <t>온도 반영:     S(T)/Sy(T)/E(T)를 [물성DB] 표에서 온도 선형보간 (204°C 초과 무효)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="inlineStr"/>
+      <c r="A16" s="62" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="A17" s="63" t="inlineStr">
         <is>
           <t>■ 시트 구성</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
-        <is>
-          <t>계산기   — 입력/결과 (메인)</t>
+      <c r="A18" s="62" t="inlineStr">
+        <is>
+          <t>계산기     — 입력/결과 (메인). 여기서만 입력합니다.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
-        <is>
-          <t>물성DB   — S(T)/Sy(T)/E(T) 표 (코드 연도판으로 교체 대상)</t>
+      <c r="A19" s="62" t="inlineStr">
+        <is>
+          <t>강도계산서 — 계산 결과를 문서 형식으로 요약 (설계조건·재료·계산결과·검증·결론·서명란).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
-        <is>
-          <t>좌굴스캔 — 좌굴 최소두께 반복해용 스캔 테이블 (수정 불필요)</t>
+      <c r="A20" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             [계산기] 입력에 자동 연동되며, A4 세로 1페이지 폭에 맞춰 인쇄됩니다.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr"/>
+      <c r="A21" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             문서정보(프로젝트명·기기번호·작성자 등) 파랑 셀은 직접 입력하세요.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="62" t="inlineStr">
+        <is>
+          <t>물성DB     — S(T)/Sy(T)/E(T) 표 (코드 연도판으로 교체 대상)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="62" t="inlineStr">
+        <is>
+          <t>좌굴스캔   — 좌굴 최소두께 반복해용 스캔 테이블 (수정 불필요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="62" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="64" t="inlineStr">
         <is>
           <t>■ 한계 및 주의</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="29" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="62" t="inlineStr">
         <is>
           <t>· 예비설계용. 정적 압력하중 전용(열응력·피로는 ALPEMA 8.1 운전제한으로 별도 관리).</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="29" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="62" t="inlineStr">
         <is>
           <t>· S/Sy/E 표는 대표값 — 적용 코드 연도판으로 반드시 검증/교체할 것.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="29" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="62" t="inlineStr">
         <is>
           <t>· 149°C 이상 장기운전은 크리프 별도 검토. Serrated/천공핀·헤더·노즐은 범위 밖.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="29" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="62" t="inlineStr">
         <is>
           <t>· 인증 설계는 ALPEMA 5.15.1.1(승인 계산법)/5.15.1.2(파열시험)으로 확정.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="29" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="62" t="inlineStr">
         <is>
           <t>· 상세 유도는 fin_thickness_derivation.md, 원본 로직은 fin_thickness_calc.py 참조.</t>
         </is>
